--- a/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="新增网点（32家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="减少网点（46家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="变更明细（30条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（32家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（28家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（30条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -478,7 +478,7 @@
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -719,23 +719,23 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>法拉利</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="C12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>-18</v>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>-100.0%</t>
+      <c r="C12" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -875,14 +875,14 @@
         <v>8626</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>8612</v>
+        <v>8630</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>-14</v>
+        <v>4</v>
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -6332,297 +6332,297 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="3" t="inlineStr">
+      <c r="A259" s="2" t="inlineStr">
         <is>
           <t>法拉利</t>
         </is>
       </c>
-      <c r="B259" s="3" t="inlineStr">
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D259" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E259" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>云南</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D260" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E260" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D261" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E261" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>四川</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D262" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E262" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>安徽</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D263" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E263" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>山东</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D264" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E264" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>广东</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D265" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E265" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>江苏</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D266" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E266" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
         <is>
           <t>浙江</t>
         </is>
       </c>
-      <c r="C259" s="3" t="n">
+      <c r="C267" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D259" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E259" s="3" t="n">
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" s="3" t="inlineStr">
+      <c r="D267" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E267" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
         <is>
           <t>法拉利</t>
         </is>
       </c>
-      <c r="B260" s="3" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="C260" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D260" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E260" s="3" t="n">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="3" t="inlineStr">
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>湖北</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D268" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E268" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
         <is>
           <t>法拉利</t>
         </is>
       </c>
-      <c r="B261" s="3" t="inlineStr">
-        <is>
-          <t>江苏</t>
-        </is>
-      </c>
-      <c r="C261" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D261" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E261" s="3" t="n">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" s="3" t="inlineStr">
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>湖南</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D269" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E269" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
         <is>
           <t>法拉利</t>
         </is>
       </c>
-      <c r="B262" s="3" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C262" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D262" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E262" s="3" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" s="3" t="inlineStr">
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>福建</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D270" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E270" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
         <is>
           <t>法拉利</t>
         </is>
       </c>
-      <c r="B263" s="3" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C263" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D263" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E263" s="3" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" s="3" t="inlineStr">
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D271" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E271" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
         <is>
           <t>法拉利</t>
         </is>
       </c>
-      <c r="B264" s="3" t="inlineStr">
-        <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="C264" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D264" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E264" s="3" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" s="3" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B265" s="3" t="inlineStr">
-        <is>
-          <t>四川</t>
-        </is>
-      </c>
-      <c r="C265" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D265" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E265" s="3" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" s="3" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B266" s="3" t="inlineStr">
-        <is>
-          <t>安徽</t>
-        </is>
-      </c>
-      <c r="C266" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D266" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E266" s="3" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" s="3" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B267" s="3" t="inlineStr">
-        <is>
-          <t>山东</t>
-        </is>
-      </c>
-      <c r="C267" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D267" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E267" s="3" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" s="3" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B268" s="3" t="inlineStr">
-        <is>
-          <t>湖北</t>
-        </is>
-      </c>
-      <c r="C268" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D268" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E268" s="3" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" s="3" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B269" s="3" t="inlineStr">
-        <is>
-          <t>湖南</t>
-        </is>
-      </c>
-      <c r="C269" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D269" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E269" s="3" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" s="3" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B270" s="3" t="inlineStr">
-        <is>
-          <t>福建</t>
-        </is>
-      </c>
-      <c r="C270" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D270" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E270" s="3" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" s="3" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B271" s="3" t="inlineStr">
-        <is>
-          <t>重庆</t>
-        </is>
-      </c>
-      <c r="C271" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D271" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E271" s="3" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" s="3" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B272" s="3" t="inlineStr">
+      <c r="B272" s="2" t="inlineStr">
         <is>
           <t>陕西</t>
         </is>
       </c>
-      <c r="C272" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D272" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E272" s="3" t="n">
-        <v>-1</v>
+      <c r="C272" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D272" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E272" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="273">
@@ -10950,7 +10950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11184,7 +11184,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙华锦绣科学园服务中心</t>
+          <t>小鹏汽车深圳坂田环城南路服务中心</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -11199,7 +11199,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>广东省深圳市龙华区观湖街道松轩社区虎地排126号锦绣二期4号楼B4层01-26号铺</t>
+          <t>深圳市龙岗区坂田街道环城南路9号高力特智慧能源产业园</t>
         </is>
       </c>
     </row>
@@ -11211,7 +11211,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田环城南路服务中心</t>
+          <t>小鹏汽车深圳龙华锦绣科学园服务中心</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>深圳市龙岗区坂田街道环城南路9号高力特智慧能源产业园</t>
+          <t>广东省深圳市龙华区观湖街道松轩社区虎地排126号锦绣二期4号楼B4层01-26号铺</t>
         </is>
       </c>
     </row>
@@ -11346,7 +11346,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>福州建发众驰4S中心</t>
+          <t>福州建发捷路4S中心</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -11361,7 +11361,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县上街镇源通东路63号</t>
+          <t>福建省福州市马尾区马尾镇马江路28号</t>
         </is>
       </c>
     </row>
@@ -11373,7 +11373,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>福州建发捷路4S中心</t>
+          <t>福州建发众驰4S中心</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -11388,842 +11388,356 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市马尾区马尾镇马江路28号</t>
+          <t>福建省福州市闽侯县上街镇源通东路63号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>意特汽车商业（上海）有限公司</t>
+          <t>深圳坪山益田假日广场</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>深圳市</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>恒通东路69号101单元 龙盛福新汇 上海 上海</t>
+          <t>广东省深圳市坪山区坪山街道六联社区深汕路（坪山段）168号益田假日世界中庭CT-L1-05号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>昆明乐骏汽车销售服务有限公司</t>
+          <t>南昌红谷滩万达广场体验店</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>昆明市</t>
+          <t>南昌市</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>滇池度假区滇池路1103号平安大厦B座1层 平安大厦 昆明市 滇池度假区</t>
+          <t>江西省南昌市红谷滩新区会展路999号万达广场</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>北京骏东汽车销售服务有限公司</t>
+          <t>理想汽车银川悠阅城零售中心</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>银川市</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>金宝街 金宝大厦一层 北京 东城区</t>
+          <t>宁夏回族自治区银川市金凤区正源南街与凤仪路交会处悠阅城1号楼1层128号商铺</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>成都骏意汽车销售服务有限公司</t>
+          <t>理想汽车东莞长安万达零售中心</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>成都市</t>
+          <t>东莞市</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>成都市高新区火车南站西路 法拉利 成都市 中国</t>
+          <t>广东省东莞市长安镇霄边社区东门中路1号长安万达广场2号门1007室</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>安徽鸿粤鸿超汽车销售服务有限公司</t>
+          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>合肥市</t>
+          <t>伊犁</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>花亭湖路与齐云山路交叉口 安徽鸿粤鸿超汽车销售服务有限公司 合肥 蜀山区</t>
+          <t>新疆伊犁哈萨克自治州伊宁市巴彦岱镇三段村资源路1号伊宁城投汽车产业园一号展厅东侧二楼202室</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>青岛恒骏汽车销售服务有限公司</t>
+          <t>理想汽车毕节双山国际汽车城授权钣喷中心（荣信店）</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>青岛市</t>
+          <t>毕节市</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>青岛市市南区东海西路1号1号楼丙户 青岛市 市南区</t>
+          <t>贵州省毕节市七星关区响水乡吊兰社区小瓦路8号双山国际汽车城1-1号商铺</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>广东骏佳汽车服务有限公司</t>
+          <t>理想汽车贵阳花溪临时交付中心</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>广州市</t>
+          <t>贵阳市</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>天河区珠江新城清风街1-48号 新世界广场首层 Guangzhou</t>
+          <t>贵阳市花溪区孟关乡孟关村 A-22</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>骏佳行汽车服务（深圳）有限公司</t>
+          <t>理想汽车大连华南万象汇零售中心</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>深圳市</t>
+          <t>大连市</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>中心路1号 深圳湾壹号北区2栋 Shenzhen Nanshan District</t>
+          <t>辽宁省大连市甘井子区山东路 350 号、352 号 华润置地 大连华南万象汇 的 LG203</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>阿斯顿·马丁</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>南京瑞骏汽车销售服务有限公司</t>
+          <t>阿斯顿·马丁北京</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>南京市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>长江路100号 长江会 南京 玄武</t>
+          <t>东城区金宝街99号 , 北京, 100005</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>阿斯顿·马丁</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>苏州意骏汽车销售服务有限公司</t>
+          <t>阿斯顿·马丁北京售后服务中心</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>苏州市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>苏州工业园区思安街99号协鑫广场西侧1F Suzhou</t>
+          <t>大兴区金时大街7号院5号楼, 北京, 100076</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>宁波骏意汽车服务有限公司</t>
+          <t>鸿蒙智行尚界用户中心•运城机场大道</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>宁波市</t>
+          <t>运城市</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>中官新路 A号楼 Ningbo Jiangbei District</t>
+          <t>山西省运城市盐湖区机场大道与库东路交叉口西南160米</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>杭州骏意汽车销售服务有限公司</t>
+          <t>华为智能生活馆•邢台逗号立方</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>杭州市</t>
+          <t>邢台市</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>浙江省杭州市南山路 杭州 上城区</t>
+          <t>河北省邢台市信都区中兴西大街逗号立方购物公园1F</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>温州骏意汽车服务有限公司</t>
+          <t>华为智能生活馆•武汉经开永旺梦乐城</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>温州市</t>
+          <t>武汉市</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>温州经济技术开发区滨海园区 3号4S店东侧 温州 中国</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>武汉骏东汽车销售服务有限公司</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>湖北</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>武汉市</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>解放大道634号K11步行街 108-109 武汉 中国</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>长沙市骏马汽车销售服务有限公司</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>湖南</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>长沙市</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>潇湘北路 圆泰长沙印 103-1 号 长沙市 中国</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>福建骏佳行汽车销售服务有限公司</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>福建</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>厦门市</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>环岛东路1821号 中航紫金广场商业街 厦门市 思明区</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>重庆骏东汽车销售服务有限公司</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>重庆</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>重庆两江新区新南路 龙湖晶郦馆A栋-1F-03b Chongqing New South St</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>陕西</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>西安市</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>深圳坪山益田假日广场</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>深圳市</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>广东省深圳市坪山区坪山街道六联社区深汕路（坪山段）168号益田假日世界中庭CT-L1-05号</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>南昌红谷滩万达广场体验店</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>江西</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>南昌市</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>江西省南昌市红谷滩新区会展路999号万达广场</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>理想汽车银川悠阅城零售中心</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>宁夏</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>银川市</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>宁夏回族自治区银川市金凤区正源南街与凤仪路交会处悠阅城1号楼1层128号商铺</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>理想汽车东莞长安万达零售中心</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>东莞市</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>广东省东莞市长安镇霄边社区东门中路1号长安万达广场2号门1007室</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>新疆</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>伊犁</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>新疆伊犁哈萨克自治州伊宁市巴彦岱镇三段村资源路1号伊宁城投汽车产业园一号展厅东侧二楼202室</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>理想汽车毕节双山国际汽车城授权钣喷中心（荣信店）</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>贵州</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>毕节市</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>贵州省毕节市七星关区响水乡吊兰社区小瓦路8号双山国际汽车城1-1号商铺</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>理想汽车贵阳花溪临时交付中心</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>贵州</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>贵阳市</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>贵阳市花溪区孟关乡孟关村 A-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>理想汽车大连华南万象汇零售中心</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>辽宁</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>大连市</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>辽宁省大连市甘井子区山东路 350 号、352 号 华润置地 大连华南万象汇 的 LG203</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>阿斯顿·马丁</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>阿斯顿·马丁北京售后服务中心</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>北京市</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>大兴区金时大街7号院5号楼, 北京, 100076</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>阿斯顿·马丁</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>阿斯顿·马丁北京</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>北京市</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>东城区金宝街99号 , 北京, 100005</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行尚界用户中心•运城机场大道</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>山西</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>运城市</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>山西省运城市盐湖区机场大道与库东路交叉口西南160米</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>华为智能生活馆•邢台逗号立方</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>河北</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>邢台市</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t>河北省邢台市信都区中兴西大街逗号立方购物公园1F</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>华为智能生活馆•武汉经开永旺梦乐城</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>湖北</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>武汉市</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>武汉经济技术开发区江城大道永旺梦乐城NO.B113b</t>
         </is>
@@ -12286,22 +11800,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12311,29 +11825,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
+          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12343,29 +11857,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
+          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>鸿蒙智行尚界用户中心•嘉兴南溪东路</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>鸿蒙智行尚界用户中心•嘉兴南溪东路</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12375,29 +11889,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
+          <t>浙江省嘉兴市南湖区大桥镇南溪东路1362号0003幢（临时营业） → 浙江省嘉兴市南湖区南溪东路1362号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12407,29 +11921,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
+          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>AITO授权用户中心•余慈鑫时代</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>AITO授权用户中心•余慈鑫时代</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12439,29 +11953,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
+          <t>慈溪市横河镇前应路1176号 → 浙江省慈溪市横河镇前应路1176号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳华通汽车城</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳华通汽车城</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12471,7 +11985,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>贵州省贵阳市云岩区金阳南路118号华通汽车城（临时营业） → 贵州省贵阳市云岩区金阳南路118号</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
@@ -12483,17 +11997,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12503,29 +12017,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
+          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12535,7 +12049,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
+          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
@@ -12547,17 +12061,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•惠州惠博大道</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•惠州惠博大道</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12567,29 +12081,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>广东省惠州市江北西区7号小区D1（金山汽车城内） → 广东省惠州市惠城区惠博大道江北西部7号小区金山汽车城3街1号B展场</t>
+          <t>广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业） → 广西壮族自治区南宁市兴宁区三塘镇兴工北路汽车市场17-27号（临时营业）</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12599,29 +12113,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业） → 广西壮族自治区南宁市兴宁区三塘镇兴工北路汽车市场17-27号（临时营业）</t>
+          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>AITO授权用户中心•贵阳华通汽车城</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>AITO授权用户中心•贵阳华通汽车城</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12631,14 +12145,14 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
+          <t>贵州省贵阳市云岩区金阳南路118号华通汽车城（临时营业） → 贵州省贵阳市云岩区金阳南路118号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -12648,12 +12162,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12663,29 +12177,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
+          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•余慈鑫时代</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•余慈鑫时代</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12695,29 +12209,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>慈溪市横河镇前应路1176号 → 浙江省慈溪市横河镇前应路1176号</t>
+          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•梅州梅塘东路</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•梅州梅塘东路</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12727,29 +12241,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>广东省梅州市梅江区梅塘东路30号 → 广东省梅州市梅江区三角镇梅塘东路30号</t>
+          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•嘉兴南溪东路</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•嘉兴南溪东路</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12759,29 +12273,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区大桥镇南溪东路1362号0003幢（临时营业） → 浙江省嘉兴市南湖区南溪东路1362号</t>
+          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12791,29 +12305,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12823,29 +12337,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
+          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•惠州惠博大道</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•惠州惠博大道</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12855,29 +12369,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
+          <t>广东省惠州市江北西区7号小区D1（金山汽车城内） → 广东省惠州市惠城区惠博大道江北西部7号小区金山汽车城3街1号B展场</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12887,29 +12401,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
+          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>鸿蒙智行尚界用户中心•梅州梅塘东路</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>鸿蒙智行尚界用户中心•梅州梅塘东路</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12919,29 +12433,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
+          <t>广东省梅州市梅江区梅塘东路30号 → 广东省梅州市梅江区三角镇梅塘东路30号</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12951,7 +12465,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
+          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
         </is>
       </c>
     </row>
@@ -12990,22 +12504,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>奔驰</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>理想汽车铜仁万山授权钣喷中心（俊汇店）</t>
+          <t>宜春华宏臻汽车有限公司</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>理想汽车铜仁万山授权服务中心（俊汇店）</t>
+          <t>宜春华宏星汽车有限公司</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13022,22 +12536,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•三明北汽车城</t>
+          <t>理想汽车鹿城零售中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•三明北汽车城</t>
+          <t>理想汽车温州鹿城零售中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13054,22 +12568,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>奔驰</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>宜春华宏臻汽车有限公司</t>
+          <t>鸿蒙智行尚界用户中心•三明北汽车城</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>宜春华宏星汽车有限公司</t>
+          <t>鸿蒙智行授权用户中心•三明北汽车城</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13091,17 +12605,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鹿城零售中心</t>
+          <t>理想汽车铜仁万山授权钣喷中心（俊汇店）</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州鹿城零售中心</t>
+          <t>理想汽车铜仁万山授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13182,22 +12696,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海松江区松江印象城</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市松江区松江印象城汽车体验店</t>
+          <t>小鹏汽车周口南环服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13207,29 +12721,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 77%</t>
+          <t>店名相似度 88%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小米汽车上海松江区松江印象城</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环服务中心</t>
+          <t>小米之家上海市松江区松江印象城汽车体验店</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13239,7 +12753,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 88%</t>
+          <t>店名相似度 77%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（32家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（34家）" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（28家）" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（30条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
@@ -719,23 +719,23 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>法拉利</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n">
+      <c r="B12" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="C12" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0.0%</t>
+      <c r="C12" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
@@ -875,14 +875,14 @@
         <v>8626</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>8630</v>
+        <v>8632</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.1%</t>
         </is>
       </c>
     </row>
@@ -897,7 +897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E434"/>
+  <dimension ref="A1:E436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6626,66 +6626,66 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="3" t="inlineStr">
+      <c r="A273" s="4" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B273" s="4" t="inlineStr">
+        <is>
+          <t>河南</t>
+        </is>
+      </c>
+      <c r="C273" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D273" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E273" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="4" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B274" s="4" t="inlineStr">
+        <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="C274" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D274" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E274" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="3" t="inlineStr">
         <is>
           <t>特斯拉</t>
         </is>
       </c>
-      <c r="B273" s="3" t="inlineStr">
+      <c r="B275" s="3" t="inlineStr">
         <is>
           <t>江西</t>
         </is>
       </c>
-      <c r="C273" s="3" t="n">
+      <c r="C275" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="D273" s="3" t="n">
+      <c r="D275" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="E273" s="3" t="n">
+      <c r="E275" s="3" t="n">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" s="2" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B274" s="2" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C274" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="D274" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="E274" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" s="2" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B275" s="2" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C275" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="D275" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="E275" s="2" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="276">
@@ -6696,14 +6696,14 @@
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C276" s="2" t="n">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="D276" s="2" t="n">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="E276" s="2" t="n">
         <v>0</v>
@@ -6717,14 +6717,14 @@
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C277" s="2" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="D277" s="2" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E277" s="2" t="n">
         <v>0</v>
@@ -6738,14 +6738,14 @@
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C278" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D278" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E278" s="2" t="n">
         <v>0</v>
@@ -6759,7 +6759,7 @@
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C279" s="2" t="n">
@@ -6780,14 +6780,14 @@
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C280" s="2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D280" s="2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E280" s="2" t="n">
         <v>0</v>
@@ -6801,14 +6801,14 @@
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C281" s="2" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="D281" s="2" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="E281" s="2" t="n">
         <v>0</v>
@@ -6822,14 +6822,14 @@
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C282" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D282" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E282" s="2" t="n">
         <v>0</v>
@@ -6843,14 +6843,14 @@
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C283" s="2" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D283" s="2" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="E283" s="2" t="n">
         <v>0</v>
@@ -6864,14 +6864,14 @@
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C284" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D284" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E284" s="2" t="n">
         <v>0</v>
@@ -6885,14 +6885,14 @@
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C285" s="2" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="D285" s="2" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E285" s="2" t="n">
         <v>0</v>
@@ -6906,14 +6906,14 @@
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C286" s="2" t="n">
-        <v>62</v>
+        <v>6</v>
       </c>
       <c r="D286" s="2" t="n">
-        <v>62</v>
+        <v>6</v>
       </c>
       <c r="E286" s="2" t="n">
         <v>0</v>
@@ -6927,14 +6927,14 @@
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C287" s="2" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D287" s="2" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E287" s="2" t="n">
         <v>0</v>
@@ -6948,14 +6948,14 @@
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C288" s="2" t="n">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="D288" s="2" t="n">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="E288" s="2" t="n">
         <v>0</v>
@@ -6969,14 +6969,14 @@
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C289" s="2" t="n">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="D289" s="2" t="n">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="E289" s="2" t="n">
         <v>0</v>
@@ -6990,14 +6990,14 @@
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C290" s="2" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="D290" s="2" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="E290" s="2" t="n">
         <v>0</v>
@@ -7011,14 +7011,14 @@
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C291" s="2" t="n">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="D291" s="2" t="n">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="E291" s="2" t="n">
         <v>0</v>
@@ -7032,14 +7032,14 @@
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C292" s="2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D292" s="2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E292" s="2" t="n">
         <v>0</v>
@@ -7053,14 +7053,14 @@
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C293" s="2" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="D293" s="2" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="E293" s="2" t="n">
         <v>0</v>
@@ -7074,14 +7074,14 @@
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C294" s="2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D294" s="2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E294" s="2" t="n">
         <v>0</v>
@@ -7095,14 +7095,14 @@
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C295" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D295" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E295" s="2" t="n">
         <v>0</v>
@@ -7116,14 +7116,14 @@
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C296" s="2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D296" s="2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E296" s="2" t="n">
         <v>0</v>
@@ -7137,14 +7137,14 @@
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C297" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D297" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E297" s="2" t="n">
         <v>0</v>
@@ -7158,14 +7158,14 @@
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C298" s="2" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D298" s="2" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E298" s="2" t="n">
         <v>0</v>
@@ -7179,59 +7179,59 @@
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C299" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="D299" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E299" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>特斯拉</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C300" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D300" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E300" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="inlineStr">
+        <is>
+          <t>特斯拉</t>
+        </is>
+      </c>
+      <c r="B301" s="2" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C299" s="2" t="n">
+      <c r="C301" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D299" s="2" t="n">
+      <c r="D301" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E299" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" s="4" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B300" s="4" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="C300" s="4" t="n">
-        <v>83</v>
-      </c>
-      <c r="D300" s="4" t="n">
-        <v>84</v>
-      </c>
-      <c r="E300" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" s="4" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B301" s="4" t="inlineStr">
-        <is>
-          <t>新疆</t>
-        </is>
-      </c>
-      <c r="C301" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="D301" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="E301" s="4" t="n">
-        <v>1</v>
+      <c r="E301" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="302">
@@ -7242,59 +7242,59 @@
       </c>
       <c r="B302" s="4" t="inlineStr">
         <is>
+          <t>广东</t>
+        </is>
+      </c>
+      <c r="C302" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="D302" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="E302" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="4" t="inlineStr">
+        <is>
+          <t>特斯拉</t>
+        </is>
+      </c>
+      <c r="B303" s="4" t="inlineStr">
+        <is>
+          <t>新疆</t>
+        </is>
+      </c>
+      <c r="C303" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D303" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E303" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="4" t="inlineStr">
+        <is>
+          <t>特斯拉</t>
+        </is>
+      </c>
+      <c r="B304" s="4" t="inlineStr">
+        <is>
           <t>福建</t>
         </is>
       </c>
-      <c r="C302" s="4" t="n">
+      <c r="C304" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="D302" s="4" t="n">
+      <c r="D304" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="E302" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" s="3" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B303" s="3" t="inlineStr">
-        <is>
-          <t>贵州</t>
-        </is>
-      </c>
-      <c r="C303" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="D303" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="E303" s="3" t="n">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" s="3" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B304" s="3" t="inlineStr">
-        <is>
-          <t>宁夏</t>
-        </is>
-      </c>
-      <c r="C304" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="D304" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E304" s="3" t="n">
-        <v>-1</v>
+      <c r="E304" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="305">
@@ -7305,17 +7305,17 @@
       </c>
       <c r="B305" s="3" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C305" s="3" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D305" s="3" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E305" s="3" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="306">
@@ -7326,59 +7326,59 @@
       </c>
       <c r="B306" s="3" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C306" s="3" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="D306" s="3" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="E306" s="3" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="2" t="inlineStr">
+      <c r="A307" s="3" t="inlineStr">
         <is>
           <t>理想</t>
         </is>
       </c>
-      <c r="B307" s="2" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C307" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="D307" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="E307" s="2" t="n">
-        <v>0</v>
+      <c r="B307" s="3" t="inlineStr">
+        <is>
+          <t>新疆</t>
+        </is>
+      </c>
+      <c r="C307" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D307" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="E307" s="3" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="2" t="inlineStr">
+      <c r="A308" s="3" t="inlineStr">
         <is>
           <t>理想</t>
         </is>
       </c>
-      <c r="B308" s="2" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C308" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="D308" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="E308" s="2" t="n">
-        <v>0</v>
+      <c r="B308" s="3" t="inlineStr">
+        <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="C308" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D308" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="E308" s="3" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="309">
@@ -7389,14 +7389,14 @@
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C309" s="2" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D309" s="2" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E309" s="2" t="n">
         <v>0</v>
@@ -7410,14 +7410,14 @@
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C310" s="2" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D310" s="2" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E310" s="2" t="n">
         <v>0</v>
@@ -7431,14 +7431,14 @@
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C311" s="2" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D311" s="2" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E311" s="2" t="n">
         <v>0</v>
@@ -7452,14 +7452,14 @@
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C312" s="2" t="n">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="D312" s="2" t="n">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="E312" s="2" t="n">
         <v>0</v>
@@ -7473,14 +7473,14 @@
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C313" s="2" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D313" s="2" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E313" s="2" t="n">
         <v>0</v>
@@ -7494,14 +7494,14 @@
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C314" s="2" t="n">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="D314" s="2" t="n">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="E314" s="2" t="n">
         <v>0</v>
@@ -7515,14 +7515,14 @@
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C315" s="2" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="D315" s="2" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="E315" s="2" t="n">
         <v>0</v>
@@ -7536,14 +7536,14 @@
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C316" s="2" t="n">
-        <v>133</v>
+        <v>83</v>
       </c>
       <c r="D316" s="2" t="n">
-        <v>133</v>
+        <v>83</v>
       </c>
       <c r="E316" s="2" t="n">
         <v>0</v>
@@ -7557,14 +7557,14 @@
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C317" s="2" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="D317" s="2" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="E317" s="2" t="n">
         <v>0</v>
@@ -7578,14 +7578,14 @@
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C318" s="2" t="n">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="D318" s="2" t="n">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="E318" s="2" t="n">
         <v>0</v>
@@ -7599,14 +7599,14 @@
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C319" s="2" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D319" s="2" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="E319" s="2" t="n">
         <v>0</v>
@@ -7620,14 +7620,14 @@
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C320" s="2" t="n">
-        <v>51</v>
+        <v>105</v>
       </c>
       <c r="D320" s="2" t="n">
-        <v>51</v>
+        <v>105</v>
       </c>
       <c r="E320" s="2" t="n">
         <v>0</v>
@@ -7641,14 +7641,14 @@
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C321" s="2" t="n">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="D321" s="2" t="n">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="E321" s="2" t="n">
         <v>0</v>
@@ -7662,14 +7662,14 @@
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C322" s="2" t="n">
-        <v>113</v>
+        <v>51</v>
       </c>
       <c r="D322" s="2" t="n">
-        <v>113</v>
+        <v>51</v>
       </c>
       <c r="E322" s="2" t="n">
         <v>0</v>
@@ -7683,14 +7683,14 @@
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C323" s="2" t="n">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="D323" s="2" t="n">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="E323" s="2" t="n">
         <v>0</v>
@@ -7704,14 +7704,14 @@
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C324" s="2" t="n">
-        <v>41</v>
+        <v>113</v>
       </c>
       <c r="D324" s="2" t="n">
-        <v>41</v>
+        <v>113</v>
       </c>
       <c r="E324" s="2" t="n">
         <v>0</v>
@@ -7725,14 +7725,14 @@
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C325" s="2" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="D325" s="2" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="E325" s="2" t="n">
         <v>0</v>
@@ -7746,14 +7746,14 @@
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C326" s="2" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="D326" s="2" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="E326" s="2" t="n">
         <v>0</v>
@@ -7767,14 +7767,14 @@
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C327" s="2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D327" s="2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E327" s="2" t="n">
         <v>0</v>
@@ -7788,14 +7788,14 @@
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C328" s="2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D328" s="2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E328" s="2" t="n">
         <v>0</v>
@@ -7809,14 +7809,14 @@
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C329" s="2" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="D329" s="2" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="E329" s="2" t="n">
         <v>0</v>
@@ -7830,14 +7830,14 @@
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C330" s="2" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="D330" s="2" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="E330" s="2" t="n">
         <v>0</v>
@@ -7851,14 +7851,14 @@
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C331" s="2" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D331" s="2" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="E331" s="2" t="n">
         <v>0</v>
@@ -7872,80 +7872,80 @@
       </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C332" s="2" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="D332" s="2" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E332" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="4" t="inlineStr">
+      <c r="A333" s="2" t="inlineStr">
         <is>
           <t>理想</t>
         </is>
       </c>
-      <c r="B333" s="4" t="inlineStr">
-        <is>
-          <t>安徽</t>
-        </is>
-      </c>
-      <c r="C333" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="D333" s="4" t="n">
-        <v>46</v>
-      </c>
-      <c r="E333" s="4" t="n">
-        <v>1</v>
+      <c r="B333" s="2" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C333" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D333" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E333" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C334" s="2" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="D334" s="2" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E334" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="2" t="inlineStr">
-        <is>
-          <t>蔚来</t>
-        </is>
-      </c>
-      <c r="B335" s="2" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C335" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="D335" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="E335" s="2" t="n">
-        <v>0</v>
+      <c r="A335" s="4" t="inlineStr">
+        <is>
+          <t>理想</t>
+        </is>
+      </c>
+      <c r="B335" s="4" t="inlineStr">
+        <is>
+          <t>安徽</t>
+        </is>
+      </c>
+      <c r="C335" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="D335" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="E335" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="336">
@@ -7956,14 +7956,14 @@
       </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C336" s="2" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="D336" s="2" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="E336" s="2" t="n">
         <v>0</v>
@@ -7977,14 +7977,14 @@
       </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C337" s="2" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D337" s="2" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E337" s="2" t="n">
         <v>0</v>
@@ -7998,14 +7998,14 @@
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C338" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D338" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E338" s="2" t="n">
         <v>0</v>
@@ -8019,14 +8019,14 @@
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C339" s="2" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D339" s="2" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E339" s="2" t="n">
         <v>0</v>
@@ -8040,14 +8040,14 @@
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C340" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D340" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E340" s="2" t="n">
         <v>0</v>
@@ -8061,14 +8061,14 @@
       </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C341" s="2" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="D341" s="2" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="E341" s="2" t="n">
         <v>0</v>
@@ -8082,14 +8082,14 @@
       </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C342" s="2" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="D342" s="2" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E342" s="2" t="n">
         <v>0</v>
@@ -8103,14 +8103,14 @@
       </c>
       <c r="B343" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C343" s="2" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D343" s="2" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="E343" s="2" t="n">
         <v>0</v>
@@ -8124,14 +8124,14 @@
       </c>
       <c r="B344" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C344" s="2" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D344" s="2" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="E344" s="2" t="n">
         <v>0</v>
@@ -8145,14 +8145,14 @@
       </c>
       <c r="B345" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C345" s="2" t="n">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="D345" s="2" t="n">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="E345" s="2" t="n">
         <v>0</v>
@@ -8166,14 +8166,14 @@
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C346" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D346" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E346" s="2" t="n">
         <v>0</v>
@@ -8187,14 +8187,14 @@
       </c>
       <c r="B347" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C347" s="2" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="D347" s="2" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="E347" s="2" t="n">
         <v>0</v>
@@ -8208,14 +8208,14 @@
       </c>
       <c r="B348" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C348" s="2" t="n">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="D348" s="2" t="n">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="E348" s="2" t="n">
         <v>0</v>
@@ -8229,14 +8229,14 @@
       </c>
       <c r="B349" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C349" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D349" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E349" s="2" t="n">
         <v>0</v>
@@ -8250,14 +8250,14 @@
       </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C350" s="2" t="n">
-        <v>13</v>
+        <v>77</v>
       </c>
       <c r="D350" s="2" t="n">
-        <v>13</v>
+        <v>77</v>
       </c>
       <c r="E350" s="2" t="n">
         <v>0</v>
@@ -8271,14 +8271,14 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C351" s="2" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D351" s="2" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E351" s="2" t="n">
         <v>0</v>
@@ -8292,14 +8292,14 @@
       </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C352" s="2" t="n">
-        <v>87</v>
+        <v>13</v>
       </c>
       <c r="D352" s="2" t="n">
-        <v>87</v>
+        <v>13</v>
       </c>
       <c r="E352" s="2" t="n">
         <v>0</v>
@@ -8313,14 +8313,14 @@
       </c>
       <c r="B353" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C353" s="2" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D353" s="2" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E353" s="2" t="n">
         <v>0</v>
@@ -8334,14 +8334,14 @@
       </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C354" s="2" t="n">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="D354" s="2" t="n">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="E354" s="2" t="n">
         <v>0</v>
@@ -8355,14 +8355,14 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C355" s="2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D355" s="2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E355" s="2" t="n">
         <v>0</v>
@@ -8376,14 +8376,14 @@
       </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C356" s="2" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D356" s="2" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E356" s="2" t="n">
         <v>0</v>
@@ -8397,14 +8397,14 @@
       </c>
       <c r="B357" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C357" s="2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D357" s="2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E357" s="2" t="n">
         <v>0</v>
@@ -8418,14 +8418,14 @@
       </c>
       <c r="B358" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C358" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D358" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E358" s="2" t="n">
         <v>0</v>
@@ -8439,14 +8439,14 @@
       </c>
       <c r="B359" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C359" s="2" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D359" s="2" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E359" s="2" t="n">
         <v>0</v>
@@ -8460,14 +8460,14 @@
       </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C360" s="2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D360" s="2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E360" s="2" t="n">
         <v>0</v>
@@ -8481,14 +8481,14 @@
       </c>
       <c r="B361" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C361" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D361" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E361" s="2" t="n">
         <v>0</v>
@@ -8502,14 +8502,14 @@
       </c>
       <c r="B362" s="2" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C362" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D362" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E362" s="2" t="n">
         <v>0</v>
@@ -8523,49 +8523,49 @@
       </c>
       <c r="B363" s="2" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C363" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D363" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E363" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="3" t="inlineStr">
-        <is>
-          <t>阿斯顿·马丁</t>
-        </is>
-      </c>
-      <c r="B364" s="3" t="inlineStr">
-        <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="C364" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D364" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E364" s="3" t="n">
-        <v>-2</v>
+      <c r="A364" s="2" t="inlineStr">
+        <is>
+          <t>蔚来</t>
+        </is>
+      </c>
+      <c r="B364" s="2" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C364" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D364" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E364" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B365" s="2" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C365" s="2" t="n">
@@ -8579,24 +8579,24 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="2" t="inlineStr">
+      <c r="A366" s="3" t="inlineStr">
         <is>
           <t>阿斯顿·马丁</t>
         </is>
       </c>
-      <c r="B366" s="2" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C366" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D366" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E366" s="2" t="n">
-        <v>0</v>
+      <c r="B366" s="3" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C366" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D366" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E366" s="3" t="n">
+        <v>-2</v>
       </c>
     </row>
     <row r="367">
@@ -8607,14 +8607,14 @@
       </c>
       <c r="B367" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C367" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D367" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E367" s="2" t="n">
         <v>0</v>
@@ -8628,14 +8628,14 @@
       </c>
       <c r="B368" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C368" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D368" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E368" s="2" t="n">
         <v>0</v>
@@ -8649,14 +8649,14 @@
       </c>
       <c r="B369" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C369" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D369" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E369" s="2" t="n">
         <v>0</v>
@@ -8670,14 +8670,14 @@
       </c>
       <c r="B370" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C370" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D370" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E370" s="2" t="n">
         <v>0</v>
@@ -8691,14 +8691,14 @@
       </c>
       <c r="B371" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C371" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D371" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E371" s="2" t="n">
         <v>0</v>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="B372" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C372" s="2" t="n">
@@ -8726,66 +8726,66 @@
       </c>
     </row>
     <row r="373">
-      <c r="A373" s="4" t="inlineStr">
+      <c r="A373" s="2" t="inlineStr">
         <is>
           <t>阿斯顿·马丁</t>
         </is>
       </c>
-      <c r="B373" s="4" t="inlineStr">
-        <is>
-          <t>江苏</t>
-        </is>
-      </c>
-      <c r="C373" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D373" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E373" s="4" t="n">
-        <v>1</v>
+      <c r="B373" s="2" t="inlineStr">
+        <is>
+          <t>贵州</t>
+        </is>
+      </c>
+      <c r="C373" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D373" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E373" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>阿斯顿·马丁</t>
         </is>
       </c>
       <c r="B374" s="2" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C374" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D374" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E374" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="375">
-      <c r="A375" s="2" t="inlineStr">
-        <is>
-          <t>雷克萨斯</t>
-        </is>
-      </c>
-      <c r="B375" s="2" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C375" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D375" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E375" s="2" t="n">
-        <v>0</v>
+      <c r="A375" s="4" t="inlineStr">
+        <is>
+          <t>阿斯顿·马丁</t>
+        </is>
+      </c>
+      <c r="B375" s="4" t="inlineStr">
+        <is>
+          <t>江苏</t>
+        </is>
+      </c>
+      <c r="C375" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D375" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E375" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="376">
@@ -8796,14 +8796,14 @@
       </c>
       <c r="B376" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C376" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D376" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E376" s="2" t="n">
         <v>0</v>
@@ -8817,14 +8817,14 @@
       </c>
       <c r="B377" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C377" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D377" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E377" s="2" t="n">
         <v>0</v>
@@ -8838,14 +8838,14 @@
       </c>
       <c r="B378" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C378" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D378" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E378" s="2" t="n">
         <v>0</v>
@@ -8859,14 +8859,14 @@
       </c>
       <c r="B379" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C379" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D379" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E379" s="2" t="n">
         <v>0</v>
@@ -8880,14 +8880,14 @@
       </c>
       <c r="B380" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C380" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D380" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E380" s="2" t="n">
         <v>0</v>
@@ -8901,14 +8901,14 @@
       </c>
       <c r="B381" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C381" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D381" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E381" s="2" t="n">
         <v>0</v>
@@ -8922,14 +8922,14 @@
       </c>
       <c r="B382" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C382" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D382" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E382" s="2" t="n">
         <v>0</v>
@@ -8943,14 +8943,14 @@
       </c>
       <c r="B383" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C383" s="2" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D383" s="2" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E383" s="2" t="n">
         <v>0</v>
@@ -8964,14 +8964,14 @@
       </c>
       <c r="B384" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C384" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D384" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E384" s="2" t="n">
         <v>0</v>
@@ -8985,14 +8985,14 @@
       </c>
       <c r="B385" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C385" s="2" t="n">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="D385" s="2" t="n">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="E385" s="2" t="n">
         <v>0</v>
@@ -9006,14 +9006,14 @@
       </c>
       <c r="B386" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C386" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D386" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E386" s="2" t="n">
         <v>0</v>
@@ -9027,14 +9027,14 @@
       </c>
       <c r="B387" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C387" s="2" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="D387" s="2" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="E387" s="2" t="n">
         <v>0</v>
@@ -9048,14 +9048,14 @@
       </c>
       <c r="B388" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C388" s="2" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="D388" s="2" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="E388" s="2" t="n">
         <v>0</v>
@@ -9069,14 +9069,14 @@
       </c>
       <c r="B389" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C389" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D389" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E389" s="2" t="n">
         <v>0</v>
@@ -9090,14 +9090,14 @@
       </c>
       <c r="B390" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C390" s="2" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="D390" s="2" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E390" s="2" t="n">
         <v>0</v>
@@ -9111,14 +9111,14 @@
       </c>
       <c r="B391" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C391" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D391" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E391" s="2" t="n">
         <v>0</v>
@@ -9132,14 +9132,14 @@
       </c>
       <c r="B392" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C392" s="2" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D392" s="2" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="E392" s="2" t="n">
         <v>0</v>
@@ -9153,14 +9153,14 @@
       </c>
       <c r="B393" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C393" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D393" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E393" s="2" t="n">
         <v>0</v>
@@ -9174,14 +9174,14 @@
       </c>
       <c r="B394" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C394" s="2" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="D394" s="2" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="E394" s="2" t="n">
         <v>0</v>
@@ -9195,14 +9195,14 @@
       </c>
       <c r="B395" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C395" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D395" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E395" s="2" t="n">
         <v>0</v>
@@ -9216,14 +9216,14 @@
       </c>
       <c r="B396" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C396" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D396" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E396" s="2" t="n">
         <v>0</v>
@@ -9237,14 +9237,14 @@
       </c>
       <c r="B397" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C397" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D397" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E397" s="2" t="n">
         <v>0</v>
@@ -9258,14 +9258,14 @@
       </c>
       <c r="B398" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C398" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D398" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E398" s="2" t="n">
         <v>0</v>
@@ -9279,14 +9279,14 @@
       </c>
       <c r="B399" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C399" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D399" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E399" s="2" t="n">
         <v>0</v>
@@ -9300,7 +9300,7 @@
       </c>
       <c r="B400" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C400" s="2" t="n">
@@ -9321,14 +9321,14 @@
       </c>
       <c r="B401" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C401" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D401" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E401" s="2" t="n">
         <v>0</v>
@@ -9342,14 +9342,14 @@
       </c>
       <c r="B402" s="2" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C402" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D402" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E402" s="2" t="n">
         <v>0</v>
@@ -9363,59 +9363,59 @@
       </c>
       <c r="B403" s="2" t="inlineStr">
         <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C403" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D403" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E403" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="2" t="inlineStr">
+        <is>
+          <t>雷克萨斯</t>
+        </is>
+      </c>
+      <c r="B404" s="2" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C404" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D404" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E404" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="2" t="inlineStr">
+        <is>
+          <t>雷克萨斯</t>
+        </is>
+      </c>
+      <c r="B405" s="2" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C403" s="2" t="n">
+      <c r="C405" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D403" s="2" t="n">
+      <c r="D405" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E403" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="404">
-      <c r="A404" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B404" s="3" t="inlineStr">
-        <is>
-          <t>山西</t>
-        </is>
-      </c>
-      <c r="C404" s="3" t="n">
-        <v>43</v>
-      </c>
-      <c r="D404" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="E404" s="3" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="405">
-      <c r="A405" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B405" s="3" t="inlineStr">
-        <is>
-          <t>河北</t>
-        </is>
-      </c>
-      <c r="C405" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="D405" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="E405" s="3" t="n">
-        <v>-1</v>
+      <c r="E405" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="406">
@@ -9426,59 +9426,59 @@
       </c>
       <c r="B406" s="3" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C406" s="3" t="n">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="D406" s="3" t="n">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="E406" s="3" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="407">
-      <c r="A407" s="2" t="inlineStr">
+      <c r="A407" s="3" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B407" s="2" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C407" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="D407" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="E407" s="2" t="n">
-        <v>0</v>
+      <c r="B407" s="3" t="inlineStr">
+        <is>
+          <t>河北</t>
+        </is>
+      </c>
+      <c r="C407" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="D407" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="E407" s="3" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="408">
-      <c r="A408" s="2" t="inlineStr">
+      <c r="A408" s="3" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B408" s="2" t="inlineStr">
-        <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="C408" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="D408" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="E408" s="2" t="n">
-        <v>0</v>
+      <c r="B408" s="3" t="inlineStr">
+        <is>
+          <t>湖北</t>
+        </is>
+      </c>
+      <c r="C408" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="D408" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="E408" s="3" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="409">
@@ -9489,14 +9489,14 @@
       </c>
       <c r="B409" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C409" s="2" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="D409" s="2" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="E409" s="2" t="n">
         <v>0</v>
@@ -9510,14 +9510,14 @@
       </c>
       <c r="B410" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C410" s="2" t="n">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="D410" s="2" t="n">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="E410" s="2" t="n">
         <v>0</v>
@@ -9531,14 +9531,14 @@
       </c>
       <c r="B411" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C411" s="2" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D411" s="2" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E411" s="2" t="n">
         <v>0</v>
@@ -9552,14 +9552,14 @@
       </c>
       <c r="B412" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C412" s="2" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="D412" s="2" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="E412" s="2" t="n">
         <v>0</v>
@@ -9573,14 +9573,14 @@
       </c>
       <c r="B413" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C413" s="2" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D413" s="2" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="E413" s="2" t="n">
         <v>0</v>
@@ -9594,14 +9594,14 @@
       </c>
       <c r="B414" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C414" s="2" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="D414" s="2" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="E414" s="2" t="n">
         <v>0</v>
@@ -9615,14 +9615,14 @@
       </c>
       <c r="B415" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C415" s="2" t="n">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="D415" s="2" t="n">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="E415" s="2" t="n">
         <v>0</v>
@@ -9636,14 +9636,14 @@
       </c>
       <c r="B416" s="2" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C416" s="2" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D416" s="2" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E416" s="2" t="n">
         <v>0</v>
@@ -9657,14 +9657,14 @@
       </c>
       <c r="B417" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C417" s="2" t="n">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="D417" s="2" t="n">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="E417" s="2" t="n">
         <v>0</v>
@@ -9678,14 +9678,14 @@
       </c>
       <c r="B418" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C418" s="2" t="n">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="D418" s="2" t="n">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="E418" s="2" t="n">
         <v>0</v>
@@ -9699,14 +9699,14 @@
       </c>
       <c r="B419" s="2" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C419" s="2" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="D419" s="2" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="E419" s="2" t="n">
         <v>0</v>
@@ -9720,59 +9720,59 @@
       </c>
       <c r="B420" s="2" t="inlineStr">
         <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C420" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="D420" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="E420" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B421" s="2" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C421" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D421" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E421" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B422" s="2" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C420" s="2" t="n">
+      <c r="C422" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="D420" s="2" t="n">
+      <c r="D422" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="E420" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="421">
-      <c r="A421" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B421" s="4" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C421" s="4" t="n">
-        <v>66</v>
-      </c>
-      <c r="D421" s="4" t="n">
-        <v>67</v>
-      </c>
-      <c r="E421" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="422">
-      <c r="A422" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B422" s="4" t="inlineStr">
-        <is>
-          <t>内蒙古</t>
-        </is>
-      </c>
-      <c r="C422" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="D422" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="E422" s="4" t="n">
-        <v>1</v>
+      <c r="E422" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="423">
@@ -9783,14 +9783,14 @@
       </c>
       <c r="B423" s="4" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C423" s="4" t="n">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="D423" s="4" t="n">
-        <v>93</v>
+        <v>67</v>
       </c>
       <c r="E423" s="4" t="n">
         <v>1</v>
@@ -9804,14 +9804,14 @@
       </c>
       <c r="B424" s="4" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C424" s="4" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D424" s="4" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="E424" s="4" t="n">
         <v>1</v>
@@ -9825,14 +9825,14 @@
       </c>
       <c r="B425" s="4" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C425" s="4" t="n">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="D425" s="4" t="n">
-        <v>14</v>
+        <v>93</v>
       </c>
       <c r="E425" s="4" t="n">
         <v>1</v>
@@ -9846,14 +9846,14 @@
       </c>
       <c r="B426" s="4" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C426" s="4" t="n">
-        <v>205</v>
+        <v>22</v>
       </c>
       <c r="D426" s="4" t="n">
-        <v>206</v>
+        <v>23</v>
       </c>
       <c r="E426" s="4" t="n">
         <v>1</v>
@@ -9867,14 +9867,14 @@
       </c>
       <c r="B427" s="4" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C427" s="4" t="n">
-        <v>142</v>
+        <v>13</v>
       </c>
       <c r="D427" s="4" t="n">
-        <v>143</v>
+        <v>14</v>
       </c>
       <c r="E427" s="4" t="n">
         <v>1</v>
@@ -9888,14 +9888,14 @@
       </c>
       <c r="B428" s="4" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C428" s="4" t="n">
-        <v>84</v>
+        <v>205</v>
       </c>
       <c r="D428" s="4" t="n">
-        <v>85</v>
+        <v>206</v>
       </c>
       <c r="E428" s="4" t="n">
         <v>1</v>
@@ -9909,14 +9909,14 @@
       </c>
       <c r="B429" s="4" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C429" s="4" t="n">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="D429" s="4" t="n">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="E429" s="4" t="n">
         <v>1</v>
@@ -9930,14 +9930,14 @@
       </c>
       <c r="B430" s="4" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C430" s="4" t="n">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="D430" s="4" t="n">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="E430" s="4" t="n">
         <v>1</v>
@@ -9951,14 +9951,14 @@
       </c>
       <c r="B431" s="4" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C431" s="4" t="n">
-        <v>39</v>
+        <v>151</v>
       </c>
       <c r="D431" s="4" t="n">
-        <v>40</v>
+        <v>152</v>
       </c>
       <c r="E431" s="4" t="n">
         <v>1</v>
@@ -9972,14 +9972,14 @@
       </c>
       <c r="B432" s="4" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C432" s="4" t="n">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="D432" s="4" t="n">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="E432" s="4" t="n">
         <v>1</v>
@@ -9993,17 +9993,17 @@
       </c>
       <c r="B433" s="4" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C433" s="4" t="n">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="D433" s="4" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E433" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="434">
@@ -10014,16 +10014,58 @@
       </c>
       <c r="B434" s="4" t="inlineStr">
         <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="C434" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="D434" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="E434" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="4" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B435" s="4" t="inlineStr">
+        <is>
+          <t>安徽</t>
+        </is>
+      </c>
+      <c r="C435" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="D435" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="E435" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="4" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B436" s="4" t="inlineStr">
+        <is>
           <t>山东</t>
         </is>
       </c>
-      <c r="C434" s="4" t="n">
+      <c r="C436" s="4" t="n">
         <v>104</v>
       </c>
-      <c r="D434" s="4" t="n">
+      <c r="D436" s="4" t="n">
         <v>106</v>
       </c>
-      <c r="E434" s="4" t="n">
+      <c r="E436" s="4" t="n">
         <v>2</v>
       </c>
     </row>
@@ -10038,7 +10080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10321,54 +10363,54 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心体验店L123</t>
+          <t>郑州悦骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>深圳市</t>
+          <t>郑州市</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>广东省深圳市福田区福华路与岗厦二路交叉口卓悦中心</t>
+          <t>如意西路 中国平煤神马集团 郑州 郑东新区</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>茂名茂悦东荟城城市展厅L1-1292</t>
+          <t>沈阳鸿粤鸿福汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>茂名市</t>
+          <t>沈阳市</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>广东省茂名市茂南区油城十路与茂名大道交汇处东汇城L1层1292-293、1294-2商铺</t>
+          <t>浑南区全运路 Shenyang China</t>
         </is>
       </c>
     </row>
@@ -10380,22 +10422,22 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>库尔勒汇嘉时代</t>
+          <t>深圳福田卓悦中心体验店L123</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>巴音郭楞蒙古自治州</t>
+          <t>深圳市</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区巴音郭楞蒙古自治州团结辖区朝阳路9库尔勒汇嘉号时代购物中心一楼DJL1006/DJL1007</t>
+          <t>广东省深圳市福田区福华路与岗厦二路交叉口卓悦中心</t>
         </is>
       </c>
     </row>
@@ -10407,157 +10449,157 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>莆田城厢万达广场</t>
+          <t>茂名茂悦东荟城城市展厅L1-1292</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>莆田市</t>
+          <t>茂名市</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>福建省莆田市城厢区荔华东大道8号万达广场F1YX-ZT-002号展位</t>
+          <t>广东省茂名市茂南区油城十路与茂名大道交汇处东汇城L1层1292-293、1294-2商铺</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>理想汽车芜湖祥盛路零售中心</t>
+          <t>库尔勒汇嘉时代</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>芜湖市</t>
+          <t>巴音郭楞蒙古自治州</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>安徽省芜湖市鸠兹家苑汽车园祥盛路57号</t>
+          <t>新疆维吾尔自治区巴音郭楞蒙古自治州团结辖区朝阳路9库尔勒汇嘉号时代购物中心一楼DJL1006/DJL1007</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>理想汽车江门蓬江临时交付中心</t>
+          <t>莆田城厢万达广场</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>江门市</t>
+          <t>莆田市</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>江门市蓬江区建设三路54号</t>
+          <t>福建省莆田市城厢区荔华东大道8号万达广场F1YX-ZT-002号展位</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁苏州</t>
+          <t>理想汽车芜湖祥盛路零售中心</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>苏州市</t>
+          <t>芜湖市</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>苏州工业园区苏州大道东418号L101, 江苏省苏州市, 125127</t>
+          <t>安徽省芜湖市鸠兹家苑汽车园祥盛路57号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（宜家荟聚）</t>
+          <t>理想汽车江门蓬江临时交付中心</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>江门市</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>上海市长宁区金钟路788号01C04A 华为</t>
+          <t>江门市蓬江区建设三路54号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>阿斯顿·马丁</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
+          <t>阿斯顿·马丁苏州</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>鄂尔多斯市</t>
+          <t>苏州市</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼</t>
+          <t>苏州工业园区苏州大道东418号L101, 江苏省苏州市, 125127</t>
         </is>
       </c>
     </row>
@@ -10569,22 +10611,22 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
+          <t>华为授权体验店（宜家荟聚）</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>眉山市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>四川省眉山市东坡区眉州大道西五段99号1-2层</t>
+          <t>上海市长宁区金钟路788号01C04A 华为</t>
         </is>
       </c>
     </row>
@@ -10596,22 +10638,22 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•天津西青大寺汽车园</t>
+          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>鄂尔多斯市</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>天津市西青区大寺镇储源道17号</t>
+          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼</t>
         </is>
       </c>
     </row>
@@ -10623,22 +10665,22 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•固原九龙路</t>
+          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>固原市</t>
+          <t>眉山市</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>宁夏回族自治区固原市原州区九龙路与民族街交叉口</t>
+          <t>四川省眉山市东坡区眉州大道西五段99号1-2层</t>
         </is>
       </c>
     </row>
@@ -10650,22 +10692,22 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（八佰伴）</t>
+          <t>AITO授权用户中心•天津西青大寺汽车园</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>芜湖市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>安徽省芜湖市镜湖区银湖路八佰伴生活广场3号门一楼华为授权体验店</t>
+          <t>天津市西青区大寺镇储源道17号</t>
         </is>
       </c>
     </row>
@@ -10677,22 +10719,22 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
+          <t>鸿蒙智行授权用户中心•固原九龙路</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>芜湖市</t>
+          <t>固原市</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口</t>
+          <t>宁夏回族自治区固原市原州区九龙路与民族街交叉口</t>
         </is>
       </c>
     </row>
@@ -10704,22 +10746,22 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•滨州渤海五路</t>
+          <t>华为授权体验店（八佰伴）</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>滨州市</t>
+          <t>芜湖市</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>山东省滨州市滨城区黄河十五路渤海五路北200米路东</t>
+          <t>安徽省芜湖市镜湖区银湖路八佰伴生活广场3号门一楼华为授权体验店</t>
         </is>
       </c>
     </row>
@@ -10731,22 +10773,22 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•烟台芝罘万达</t>
+          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>烟台市</t>
+          <t>芜湖市</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>山东省烟台市芝罘区西关南街万达广场一楼华为智能生活馆</t>
+          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口</t>
         </is>
       </c>
     </row>
@@ -10758,22 +10800,22 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
+          <t>鸿蒙智行授权用户中心•滨州渤海五路</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>肇庆市</t>
+          <t>滨州市</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>广东省肇庆市肇庆大道美轮车城北区2号楼</t>
+          <t>山东省滨州市滨城区黄河十五路渤海五路北200米路东</t>
         </is>
       </c>
     </row>
@@ -10785,22 +10827,22 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•无锡八佰伴中心</t>
+          <t>华为智能生活馆•烟台芝罘万达</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>无锡市</t>
+          <t>烟台市</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>江苏省无锡市锡山区无锡八佰伴中心1F华为智能生活馆</t>
+          <t>山东省烟台市芝罘区西关南街万达广场一楼华为智能生活馆</t>
         </is>
       </c>
     </row>
@@ -10812,22 +10854,22 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•郑州华联商厦</t>
+          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>郑州市</t>
+          <t>肇庆市</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>河南省郑州市二七区二七路230号郑州华联商厦一层</t>
+          <t>广东省肇庆市肇庆大道美轮车城北区2号楼</t>
         </is>
       </c>
     </row>
@@ -10839,22 +10881,22 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•嘉兴平湖吾悦</t>
+          <t>华为智能生活馆•无锡八佰伴中心</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>嘉兴市</t>
+          <t>无锡市</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市平湖市当湖街道南市路811号吾悦广场1幢1楼1038-1商铺（内街）华为智能生活馆</t>
+          <t>江苏省无锡市锡山区无锡八佰伴中心1F华为智能生活馆</t>
         </is>
       </c>
     </row>
@@ -10866,22 +10908,22 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
+          <t>华为智能生活馆•郑州华联商厦</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>邵阳市</t>
+          <t>郑州市</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>湖南省邵阳市双清区邵阳大道东联接线交叉口天骄汽配城内东100米</t>
+          <t>河南省郑州市二七区二七路230号郑州华联商厦一层</t>
         </is>
       </c>
     </row>
@@ -10893,22 +10935,22 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•遵义汇川</t>
+          <t>华为智能生活馆•嘉兴平湖吾悦</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>遵义市</t>
+          <t>嘉兴市</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>贵州省遵义市汇川区董公寺街道和平社区汽车商贸城通源汽车文化广场内（临时营业）</t>
+          <t>浙江省嘉兴市平湖市当湖街道南市路811号吾悦广场1幢1楼1038-1商铺（内街）华为智能生活馆</t>
         </is>
       </c>
     </row>
@@ -10920,20 +10962,74 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
+          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>湖南</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>邵阳市</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>湖南省邵阳市双清区邵阳大道东联接线交叉口天骄汽配城内东100米</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>鸿蒙智行授权用户中心•遵义汇川</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>贵州</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>遵义市</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>贵州省遵义市汇川区董公寺街道和平社区汽车商贸城通源汽车文化广场内（临时营业）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
           <t>华为智能生活馆•重庆都市起点购物公园</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>重庆</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>重庆市</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>重庆市涪陵区兴华中路25号泽胜商业步行街都市起点购物公园L1层12/13/14号</t>
         </is>
@@ -11184,7 +11280,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田环城南路服务中心</t>
+          <t>小鹏汽车深圳龙华锦绣科学园服务中心</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -11199,7 +11295,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>深圳市龙岗区坂田街道环城南路9号高力特智慧能源产业园</t>
+          <t>广东省深圳市龙华区观湖街道松轩社区虎地排126号锦绣二期4号楼B4层01-26号铺</t>
         </is>
       </c>
     </row>
@@ -11211,7 +11307,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙华锦绣科学园服务中心</t>
+          <t>小鹏汽车深圳坂田环城南路服务中心</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -11226,7 +11322,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>广东省深圳市龙华区观湖街道松轩社区虎地排126号锦绣二期4号楼B4层01-26号铺</t>
+          <t>深圳市龙岗区坂田街道环城南路9号高力特智慧能源产业园</t>
         </is>
       </c>
     </row>
@@ -11346,7 +11442,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>福州建发捷路4S中心</t>
+          <t>福州建发众驰4S中心</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -11361,7 +11457,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市马尾区马尾镇马江路28号</t>
+          <t>福建省福州市闽侯县上街镇源通东路63号</t>
         </is>
       </c>
     </row>
@@ -11373,7 +11469,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>福州建发众驰4S中心</t>
+          <t>福州建发捷路4S中心</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -11388,7 +11484,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县上街镇源通东路63号</t>
+          <t>福建省福州市马尾区马尾镇马江路28号</t>
         </is>
       </c>
     </row>
@@ -11800,22 +11896,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11825,29 +11921,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
+          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>AITO授权用户中心•余慈鑫时代</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>AITO授权用户中心•余慈鑫时代</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11857,29 +11953,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
+          <t>慈溪市横河镇前应路1176号 → 浙江省慈溪市横河镇前应路1176号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•嘉兴南溪东路</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•嘉兴南溪东路</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11889,14 +11985,14 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区大桥镇南溪东路1362号0003幢（临时营业） → 浙江省嘉兴市南湖区南溪东路1362号</t>
+          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -11906,12 +12002,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11921,7 +12017,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
+          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
         </is>
       </c>
     </row>
@@ -11933,17 +12029,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•余慈鑫时代</t>
+          <t>鸿蒙智行尚界用户中心•惠州惠博大道</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•余慈鑫时代</t>
+          <t>鸿蒙智行尚界用户中心•惠州惠博大道</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11953,29 +12049,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>慈溪市横河镇前应路1176号 → 浙江省慈溪市横河镇前应路1176号</t>
+          <t>广东省惠州市江北西区7号小区D1（金山汽车城内） → 广东省惠州市惠城区惠博大道江北西部7号小区金山汽车城3街1号B展场</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11985,7 +12081,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业） → 广西壮族自治区南宁市兴宁区三塘镇兴工北路汽车市场17-27号（临时营业）</t>
         </is>
       </c>
     </row>
@@ -11997,17 +12093,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12017,29 +12113,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
+          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12049,29 +12145,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
+          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12081,7 +12177,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业） → 广西壮族自治区南宁市兴宁区三塘镇兴工北路汽车市场17-27号（临时营业）</t>
+          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
         </is>
       </c>
     </row>
@@ -12093,17 +12189,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12113,29 +12209,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
+          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳华通汽车城</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳华通汽车城</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12145,29 +12241,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>贵州省贵阳市云岩区金阳南路118号华通汽车城（临时营业） → 贵州省贵阳市云岩区金阳南路118号</t>
+          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12177,29 +12273,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
+          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12209,7 +12305,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
+          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
         </is>
       </c>
     </row>
@@ -12221,17 +12317,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12241,29 +12337,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
+          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>鸿蒙智行尚界用户中心•梅州梅塘东路</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>鸿蒙智行尚界用户中心•梅州梅塘东路</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12273,29 +12369,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
+          <t>广东省梅州市梅江区梅塘东路30号 → 广东省梅州市梅江区三角镇梅塘东路30号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12305,29 +12401,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
+          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>AITO授权用户中心•贵阳华通汽车城</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>AITO授权用户中心•贵阳华通汽车城</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12337,29 +12433,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
+          <t>贵州省贵阳市云岩区金阳南路118号华通汽车城（临时营业） → 贵州省贵阳市云岩区金阳南路118号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•惠州惠博大道</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•惠州惠博大道</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12369,7 +12465,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>广东省惠州市江北西区7号小区D1（金山汽车城内） → 广东省惠州市惠城区惠博大道江北西部7号小区金山汽车城3街1号B展场</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
@@ -12381,17 +12477,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12401,29 +12497,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
+          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•梅州梅塘东路</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•梅州梅塘东路</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12433,29 +12529,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>广东省梅州市梅江区梅塘东路30号 → 广东省梅州市梅江区三角镇梅塘东路30号</t>
+          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>鸿蒙智行尚界用户中心•嘉兴南溪东路</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>鸿蒙智行尚界用户中心•嘉兴南溪东路</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12465,7 +12561,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
+          <t>浙江省嘉兴市南湖区大桥镇南溪东路1362号0003幢（临时营业） → 浙江省嘉兴市南湖区南溪东路1362号</t>
         </is>
       </c>
     </row>
@@ -12504,22 +12600,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>奔驰</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>宜春华宏臻汽车有限公司</t>
+          <t>天津鲁能城城市中心店</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>宜春华宏星汽车有限公司</t>
+          <t>天津贵和城市中心店</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -12568,22 +12664,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•三明北汽车城</t>
+          <t>理想汽车铜仁万山授权钣喷中心（俊汇店）</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•三明北汽车城</t>
+          <t>理想汽车铜仁万山授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -12600,22 +12696,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车铜仁万山授权钣喷中心（俊汇店）</t>
+          <t>鸿蒙智行尚界用户中心•三明北汽车城</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车铜仁万山授权服务中心（俊汇店）</t>
+          <t>鸿蒙智行授权用户中心•三明北汽车城</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -12632,22 +12728,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>奔驰</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>天津鲁能城城市中心店</t>
+          <t>宜春华宏臻汽车有限公司</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>天津贵和城市中心店</t>
+          <t>宜春华宏星汽车有限公司</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -12696,22 +12792,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小米汽车上海松江区松江印象城</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环服务中心</t>
+          <t>小米之家上海市松江区松江印象城汽车体验店</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -12721,29 +12817,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 88%</t>
+          <t>店名相似度 77%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海松江区松江印象城</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市松江区松江印象城汽车体验店</t>
+          <t>小鹏汽车周口南环服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -12753,7 +12849,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 77%</t>
+          <t>店名相似度 88%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（34家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（32家）" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（28家）" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（30条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
@@ -719,23 +719,23 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>法拉利</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="C12" s="4" t="n">
+      <c r="B12" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="D12" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>11.1%</t>
+      <c r="C12" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>8626</v>
+        <v>8628</v>
       </c>
       <c r="C19" s="1" t="n">
         <v>8632</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -6507,14 +6507,14 @@
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C267" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D267" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E267" s="2" t="n">
         <v>0</v>
@@ -6528,14 +6528,14 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C268" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D268" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E268" s="2" t="n">
         <v>0</v>
@@ -6549,7 +6549,7 @@
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C269" s="2" t="n">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C270" s="2" t="n">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C271" s="2" t="n">
@@ -6612,59 +6612,59 @@
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D272" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E272" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D273" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E273" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
           <t>陕西</t>
         </is>
       </c>
-      <c r="C272" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D272" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E272" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" s="4" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B273" s="4" t="inlineStr">
-        <is>
-          <t>河南</t>
-        </is>
-      </c>
-      <c r="C273" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D273" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E273" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" s="4" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B274" s="4" t="inlineStr">
-        <is>
-          <t>辽宁</t>
-        </is>
-      </c>
-      <c r="C274" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D274" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E274" s="4" t="n">
-        <v>1</v>
+      <c r="C274" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D274" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E274" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="275">
@@ -10080,7 +10080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10363,54 +10363,54 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>郑州悦骏汽车销售服务有限公司</t>
+          <t>深圳福田卓悦中心体验店L123</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>郑州市</t>
+          <t>深圳市</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>如意西路 中国平煤神马集团 郑州 郑东新区</t>
+          <t>广东省深圳市福田区福华路与岗厦二路交叉口卓悦中心</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>沈阳鸿粤鸿福汽车销售服务有限公司</t>
+          <t>茂名茂悦东荟城城市展厅L1-1292</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>沈阳市</t>
+          <t>茂名市</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>浑南区全运路 Shenyang China</t>
+          <t>广东省茂名市茂南区油城十路与茂名大道交汇处东汇城L1层1292-293、1294-2商铺</t>
         </is>
       </c>
     </row>
@@ -10422,22 +10422,22 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心体验店L123</t>
+          <t>库尔勒汇嘉时代</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>深圳市</t>
+          <t>巴音郭楞蒙古自治州</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>广东省深圳市福田区福华路与岗厦二路交叉口卓悦中心</t>
+          <t>新疆维吾尔自治区巴音郭楞蒙古自治州团结辖区朝阳路9库尔勒汇嘉号时代购物中心一楼DJL1006/DJL1007</t>
         </is>
       </c>
     </row>
@@ -10449,157 +10449,157 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>茂名茂悦东荟城城市展厅L1-1292</t>
+          <t>莆田城厢万达广场</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>茂名市</t>
+          <t>莆田市</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>广东省茂名市茂南区油城十路与茂名大道交汇处东汇城L1层1292-293、1294-2商铺</t>
+          <t>福建省莆田市城厢区荔华东大道8号万达广场F1YX-ZT-002号展位</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>库尔勒汇嘉时代</t>
+          <t>理想汽车芜湖祥盛路零售中心</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>巴音郭楞蒙古自治州</t>
+          <t>芜湖市</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区巴音郭楞蒙古自治州团结辖区朝阳路9库尔勒汇嘉号时代购物中心一楼DJL1006/DJL1007</t>
+          <t>安徽省芜湖市鸠兹家苑汽车园祥盛路57号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>莆田城厢万达广场</t>
+          <t>理想汽车江门蓬江临时交付中心</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>莆田市</t>
+          <t>江门市</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>福建省莆田市城厢区荔华东大道8号万达广场F1YX-ZT-002号展位</t>
+          <t>江门市蓬江区建设三路54号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>阿斯顿·马丁</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>理想汽车芜湖祥盛路零售中心</t>
+          <t>阿斯顿·马丁苏州</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>芜湖市</t>
+          <t>苏州市</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>安徽省芜湖市鸠兹家苑汽车园祥盛路57号</t>
+          <t>苏州工业园区苏州大道东418号L101, 江苏省苏州市, 125127</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>理想汽车江门蓬江临时交付中心</t>
+          <t>华为授权体验店（宜家荟聚）</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>江门市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>江门市蓬江区建设三路54号</t>
+          <t>上海市长宁区金钟路788号01C04A 华为</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁苏州</t>
+          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>苏州市</t>
+          <t>鄂尔多斯市</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>苏州工业园区苏州大道东418号L101, 江苏省苏州市, 125127</t>
+          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼</t>
         </is>
       </c>
     </row>
@@ -10611,22 +10611,22 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（宜家荟聚）</t>
+          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>眉山市</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>上海市长宁区金钟路788号01C04A 华为</t>
+          <t>四川省眉山市东坡区眉州大道西五段99号1-2层</t>
         </is>
       </c>
     </row>
@@ -10638,22 +10638,22 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
+          <t>AITO授权用户中心•天津西青大寺汽车园</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>鄂尔多斯市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼</t>
+          <t>天津市西青区大寺镇储源道17号</t>
         </is>
       </c>
     </row>
@@ -10665,22 +10665,22 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
+          <t>鸿蒙智行授权用户中心•固原九龙路</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>眉山市</t>
+          <t>固原市</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>四川省眉山市东坡区眉州大道西五段99号1-2层</t>
+          <t>宁夏回族自治区固原市原州区九龙路与民族街交叉口</t>
         </is>
       </c>
     </row>
@@ -10692,22 +10692,22 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•天津西青大寺汽车园</t>
+          <t>华为授权体验店（八佰伴）</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>芜湖市</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>天津市西青区大寺镇储源道17号</t>
+          <t>安徽省芜湖市镜湖区银湖路八佰伴生活广场3号门一楼华为授权体验店</t>
         </is>
       </c>
     </row>
@@ -10719,22 +10719,22 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•固原九龙路</t>
+          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>固原市</t>
+          <t>芜湖市</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>宁夏回族自治区固原市原州区九龙路与民族街交叉口</t>
+          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口</t>
         </is>
       </c>
     </row>
@@ -10746,22 +10746,22 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（八佰伴）</t>
+          <t>鸿蒙智行授权用户中心•滨州渤海五路</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>芜湖市</t>
+          <t>滨州市</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>安徽省芜湖市镜湖区银湖路八佰伴生活广场3号门一楼华为授权体验店</t>
+          <t>山东省滨州市滨城区黄河十五路渤海五路北200米路东</t>
         </is>
       </c>
     </row>
@@ -10773,22 +10773,22 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
+          <t>华为智能生活馆•烟台芝罘万达</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>芜湖市</t>
+          <t>烟台市</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口</t>
+          <t>山东省烟台市芝罘区西关南街万达广场一楼华为智能生活馆</t>
         </is>
       </c>
     </row>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•滨州渤海五路</t>
+          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>滨州市</t>
+          <t>肇庆市</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>山东省滨州市滨城区黄河十五路渤海五路北200米路东</t>
+          <t>广东省肇庆市肇庆大道美轮车城北区2号楼</t>
         </is>
       </c>
     </row>
@@ -10827,22 +10827,22 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•烟台芝罘万达</t>
+          <t>华为智能生活馆•无锡八佰伴中心</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>烟台市</t>
+          <t>无锡市</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>山东省烟台市芝罘区西关南街万达广场一楼华为智能生活馆</t>
+          <t>江苏省无锡市锡山区无锡八佰伴中心1F华为智能生活馆</t>
         </is>
       </c>
     </row>
@@ -10854,22 +10854,22 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
+          <t>华为智能生活馆•郑州华联商厦</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>肇庆市</t>
+          <t>郑州市</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>广东省肇庆市肇庆大道美轮车城北区2号楼</t>
+          <t>河南省郑州市二七区二七路230号郑州华联商厦一层</t>
         </is>
       </c>
     </row>
@@ -10881,22 +10881,22 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•无锡八佰伴中心</t>
+          <t>华为智能生活馆•嘉兴平湖吾悦</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>无锡市</t>
+          <t>嘉兴市</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>江苏省无锡市锡山区无锡八佰伴中心1F华为智能生活馆</t>
+          <t>浙江省嘉兴市平湖市当湖街道南市路811号吾悦广场1幢1楼1038-1商铺（内街）华为智能生活馆</t>
         </is>
       </c>
     </row>
@@ -10908,22 +10908,22 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•郑州华联商厦</t>
+          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>郑州市</t>
+          <t>邵阳市</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>河南省郑州市二七区二七路230号郑州华联商厦一层</t>
+          <t>湖南省邵阳市双清区邵阳大道东联接线交叉口天骄汽配城内东100米</t>
         </is>
       </c>
     </row>
@@ -10935,22 +10935,22 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•嘉兴平湖吾悦</t>
+          <t>鸿蒙智行授权用户中心•遵义汇川</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>嘉兴市</t>
+          <t>遵义市</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市平湖市当湖街道南市路811号吾悦广场1幢1楼1038-1商铺（内街）华为智能生活馆</t>
+          <t>贵州省遵义市汇川区董公寺街道和平社区汽车商贸城通源汽车文化广场内（临时营业）</t>
         </is>
       </c>
     </row>
@@ -10962,74 +10962,20 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
+          <t>华为智能生活馆•重庆都市起点购物公园</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>邵阳市</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>湖南省邵阳市双清区邵阳大道东联接线交叉口天骄汽配城内东100米</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•遵义汇川</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>贵州</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>遵义市</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>贵州省遵义市汇川区董公寺街道和平社区汽车商贸城通源汽车文化广场内（临时营业）</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>华为智能生活馆•重庆都市起点购物公园</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>重庆</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>重庆市涪陵区兴华中路25号泽胜商业步行街都市起点购物公园L1层12/13/14号</t>
         </is>
@@ -11442,7 +11388,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>福州建发众驰4S中心</t>
+          <t>福州建发捷路4S中心</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -11457,7 +11403,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县上街镇源通东路63号</t>
+          <t>福建省福州市马尾区马尾镇马江路28号</t>
         </is>
       </c>
     </row>
@@ -11469,7 +11415,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>福州建发捷路4S中心</t>
+          <t>福州建发众驰4S中心</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -11484,7 +11430,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市马尾区马尾镇马江路28号</t>
+          <t>福建省福州市闽侯县上街镇源通东路63号</t>
         </is>
       </c>
     </row>
@@ -11901,17 +11847,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11921,29 +11867,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
+          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•余慈鑫时代</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•余慈鑫时代</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11953,29 +11899,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>慈溪市横河镇前应路1176号 → 浙江省慈溪市横河镇前应路1176号</t>
+          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11985,7 +11931,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
+          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
         </is>
       </c>
     </row>
@@ -12002,12 +11948,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12017,29 +11963,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
+          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•惠州惠博大道</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•惠州惠博大道</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12049,29 +11995,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>广东省惠州市江北西区7号小区D1（金山汽车城内） → 广东省惠州市惠城区惠博大道江北西部7号小区金山汽车城3街1号B展场</t>
+          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12081,7 +12027,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业） → 广西壮族自治区南宁市兴宁区三塘镇兴工北路汽车市场17-27号（临时营业）</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
@@ -12093,17 +12039,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12113,29 +12059,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
+          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12145,29 +12091,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
+          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>AITO授权用户中心•余慈鑫时代</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>AITO授权用户中心•余慈鑫时代</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12177,7 +12123,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
+          <t>慈溪市横河镇前应路1176号 → 浙江省慈溪市横河镇前应路1176号</t>
         </is>
       </c>
     </row>
@@ -12189,17 +12135,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12209,29 +12155,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
+          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12241,29 +12187,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
+          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>AITO授权用户中心•贵阳华通汽车城</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>AITO授权用户中心•贵阳华通汽车城</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12273,29 +12219,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
+          <t>贵州省贵阳市云岩区金阳南路118号华通汽车城（临时营业） → 贵州省贵阳市云岩区金阳南路118号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>鸿蒙智行尚界用户中心•惠州惠博大道</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>鸿蒙智行尚界用户中心•惠州惠博大道</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12305,14 +12251,14 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
+          <t>广东省惠州市江北西区7号小区D1（金山汽车城内） → 广东省惠州市惠城区惠博大道江北西部7号小区金山汽车城3街1号B展场</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -12322,12 +12268,12 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•梅州梅塘东路</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•梅州梅塘东路</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12337,7 +12283,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
+          <t>广东省梅州市梅江区梅塘东路30号 → 广东省梅州市梅江区三角镇梅塘东路30号</t>
         </is>
       </c>
     </row>
@@ -12349,17 +12295,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•梅州梅塘东路</t>
+          <t>鸿蒙智行尚界用户中心•嘉兴南溪东路</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•梅州梅塘东路</t>
+          <t>鸿蒙智行尚界用户中心•嘉兴南溪东路</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12369,29 +12315,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>广东省梅州市梅江区梅塘东路30号 → 广东省梅州市梅江区三角镇梅塘东路30号</t>
+          <t>浙江省嘉兴市南湖区大桥镇南溪东路1362号0003幢（临时营业） → 浙江省嘉兴市南湖区南溪东路1362号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12401,29 +12347,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
+          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳华通汽车城</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳华通汽车城</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12433,29 +12379,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>贵州省贵阳市云岩区金阳南路118号华通汽车城（临时营业） → 贵州省贵阳市云岩区金阳南路118号</t>
+          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12465,29 +12411,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12497,29 +12443,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
+          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12529,29 +12475,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
+          <t>广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业） → 广西壮族自治区南宁市兴宁区三塘镇兴工北路汽车市场17-27号（临时营业）</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•嘉兴南溪东路</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•嘉兴南溪东路</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12561,7 +12507,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区大桥镇南溪东路1362号0003幢（临时营业） → 浙江省嘉兴市南湖区南溪东路1362号</t>
+          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
         </is>
       </c>
     </row>
@@ -12632,22 +12578,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>奔驰</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鹿城零售中心</t>
+          <t>宜春华宏臻汽车有限公司</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州鹿城零售中心</t>
+          <t>宜春华宏星汽车有限公司</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -12696,22 +12642,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•三明北汽车城</t>
+          <t>理想汽车鹿城零售中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•三明北汽车城</t>
+          <t>理想汽车温州鹿城零售中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -12728,22 +12674,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>奔驰</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>宜春华宏臻汽车有限公司</t>
+          <t>鸿蒙智行尚界用户中心•三明北汽车城</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>宜春华宏星汽车有限公司</t>
+          <t>鸿蒙智行授权用户中心•三明北汽车城</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（32家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（28家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（30条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="新增网点（32家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="减少网点（28家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="变更明细（30条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -11226,7 +11226,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙华锦绣科学园服务中心</t>
+          <t>小鹏汽车深圳坂田环城南路服务中心</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -11241,7 +11241,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>广东省深圳市龙华区观湖街道松轩社区虎地排126号锦绣二期4号楼B4层01-26号铺</t>
+          <t>深圳市龙岗区坂田街道环城南路9号高力特智慧能源产业园</t>
         </is>
       </c>
     </row>
@@ -11253,7 +11253,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田环城南路服务中心</t>
+          <t>小鹏汽车深圳龙华锦绣科学园服务中心</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -11268,7 +11268,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>深圳市龙岗区坂田街道环城南路9号高力特智慧能源产业园</t>
+          <t>广东省深圳市龙华区观湖街道松轩社区虎地排126号锦绣二期4号楼B4层01-26号铺</t>
         </is>
       </c>
     </row>
@@ -11658,7 +11658,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁北京</t>
+          <t>阿斯顿·马丁北京售后服务中心</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -11673,7 +11673,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>东城区金宝街99号 , 北京, 100005</t>
+          <t>大兴区金时大街7号院5号楼, 北京, 100076</t>
         </is>
       </c>
     </row>
@@ -11685,7 +11685,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁北京售后服务中心</t>
+          <t>阿斯顿·马丁北京</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -11700,7 +11700,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>大兴区金时大街7号院5号楼, 北京, 100076</t>
+          <t>东城区金宝街99号 , 北京, 100005</t>
         </is>
       </c>
     </row>
@@ -11842,22 +11842,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11867,7 +11867,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
+          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
         </is>
       </c>
     </row>
@@ -11879,17 +11879,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11899,29 +11899,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11931,7 +11931,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
+          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
         </is>
       </c>
     </row>
@@ -11943,17 +11943,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11963,29 +11963,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
+          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11995,7 +11995,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
+          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
@@ -12007,17 +12007,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12027,29 +12027,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•嘉兴南溪东路</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•嘉兴南溪东路</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12059,7 +12059,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
+          <t>浙江省嘉兴市南湖区大桥镇南溪东路1362号0003幢（临时营业） → 浙江省嘉兴市南湖区南溪东路1362号</t>
         </is>
       </c>
     </row>
@@ -12071,17 +12071,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12091,29 +12091,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
+          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•余慈鑫时代</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•余慈鑫时代</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12123,29 +12123,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>慈溪市横河镇前应路1176号 → 浙江省慈溪市横河镇前应路1176号</t>
+          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>AITO授权用户中心•余慈鑫时代</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>AITO授权用户中心•余慈鑫时代</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12155,7 +12155,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
+          <t>慈溪市横河镇前应路1176号 → 浙江省慈溪市横河镇前应路1176号</t>
         </is>
       </c>
     </row>
@@ -12167,17 +12167,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12187,29 +12187,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
+          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳华通汽车城</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳华通汽车城</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12219,7 +12219,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>贵州省贵阳市云岩区金阳南路118号华通汽车城（临时营业） → 贵州省贵阳市云岩区金阳南路118号</t>
+          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
         </is>
       </c>
     </row>
@@ -12231,17 +12231,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•惠州惠博大道</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•惠州惠博大道</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12251,14 +12251,14 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>广东省惠州市江北西区7号小区D1（金山汽车城内） → 广东省惠州市惠城区惠博大道江北西部7号小区金山汽车城3街1号B展场</t>
+          <t>广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业） → 广西壮族自治区南宁市兴宁区三塘镇兴工北路汽车市场17-27号（临时营业）</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -12268,12 +12268,12 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•梅州梅塘东路</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•梅州梅塘东路</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12283,29 +12283,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>广东省梅州市梅江区梅塘东路30号 → 广东省梅州市梅江区三角镇梅塘东路30号</t>
+          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•嘉兴南溪东路</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•嘉兴南溪东路</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12315,14 +12315,14 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区大桥镇南溪东路1362号0003幢（临时营业） → 浙江省嘉兴市南湖区南溪东路1362号</t>
+          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -12332,12 +12332,12 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•梅州梅塘东路</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•梅州梅塘东路</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12347,29 +12347,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
+          <t>广东省梅州市梅江区梅塘东路30号 → 广东省梅州市梅江区三角镇梅塘东路30号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12379,29 +12379,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
+          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>鸿蒙智行尚界用户中心•惠州惠博大道</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>鸿蒙智行尚界用户中心•惠州惠博大道</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12411,29 +12411,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
+          <t>广东省惠州市江北西区7号小区D1（金山汽车城内） → 广东省惠州市惠城区惠博大道江北西部7号小区金山汽车城3街1号B展场</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>AITO授权用户中心•贵阳华通汽车城</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>AITO授权用户中心•贵阳华通汽车城</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12443,29 +12443,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
+          <t>贵州省贵阳市云岩区金阳南路118号华通汽车城（临时营业） → 贵州省贵阳市云岩区金阳南路118号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12475,29 +12475,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业） → 广西壮族自治区南宁市兴宁区三塘镇兴工北路汽车市场17-27号（临时营业）</t>
+          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12507,7 +12507,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
+          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
         </is>
       </c>
     </row>
@@ -12546,22 +12546,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>天津鲁能城城市中心店</t>
+          <t>理想汽车铜仁万山授权钣喷中心（俊汇店）</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>天津贵和城市中心店</t>
+          <t>理想汽车铜仁万山授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -12578,22 +12578,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>奔驰</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>宜春华宏臻汽车有限公司</t>
+          <t>理想汽车鹿城零售中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>宜春华宏星汽车有限公司</t>
+          <t>理想汽车温州鹿城零售中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -12610,22 +12610,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>理想汽车铜仁万山授权钣喷中心（俊汇店）</t>
+          <t>天津鲁能城城市中心店</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>理想汽车铜仁万山授权服务中心（俊汇店）</t>
+          <t>天津贵和城市中心店</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -12642,22 +12642,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鹿城零售中心</t>
+          <t>鸿蒙智行尚界用户中心•三明北汽车城</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州鹿城零售中心</t>
+          <t>鸿蒙智行授权用户中心•三明北汽车城</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -12674,22 +12674,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奔驰</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•三明北汽车城</t>
+          <t>宜春华宏臻汽车有限公司</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•三明北汽车城</t>
+          <t>宜春华宏星汽车有限公司</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
@@ -11226,7 +11226,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田环城南路服务中心</t>
+          <t>小鹏汽车深圳龙华锦绣科学园服务中心</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -11241,7 +11241,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>深圳市龙岗区坂田街道环城南路9号高力特智慧能源产业园</t>
+          <t>广东省深圳市龙华区观湖街道松轩社区虎地排126号锦绣二期4号楼B4层01-26号铺</t>
         </is>
       </c>
     </row>
@@ -11253,7 +11253,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙华锦绣科学园服务中心</t>
+          <t>小鹏汽车深圳坂田环城南路服务中心</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -11268,7 +11268,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>广东省深圳市龙华区观湖街道松轩社区虎地排126号锦绣二期4号楼B4层01-26号铺</t>
+          <t>深圳市龙岗区坂田街道环城南路9号高力特智慧能源产业园</t>
         </is>
       </c>
     </row>
@@ -11842,22 +11842,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>AITO授权用户中心•余慈鑫时代</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>AITO授权用户中心•余慈鑫时代</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11867,29 +11867,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
+          <t>慈溪市横河镇前应路1176号 → 浙江省慈溪市横河镇前应路1176号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11899,29 +11899,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11931,29 +11931,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
+          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•嘉兴南溪东路</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•嘉兴南溪东路</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11963,29 +11963,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
+          <t>浙江省嘉兴市南湖区大桥镇南溪东路1362号0003幢（临时营业） → 浙江省嘉兴市南湖区南溪东路1362号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11995,29 +11995,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
+          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12027,29 +12027,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
+          <t>广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业） → 广西壮族自治区南宁市兴宁区三塘镇兴工北路汽车市场17-27号（临时营业）</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•嘉兴南溪东路</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•嘉兴南溪东路</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12059,29 +12059,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区大桥镇南溪东路1362号0003幢（临时营业） → 浙江省嘉兴市南湖区南溪东路1362号</t>
+          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12091,7 +12091,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
+          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
         </is>
       </c>
     </row>
@@ -12103,17 +12103,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12123,29 +12123,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
+          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•余慈鑫时代</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•余慈鑫时代</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12155,7 +12155,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>慈溪市横河镇前应路1176号 → 浙江省慈溪市横河镇前应路1176号</t>
+          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
@@ -12167,17 +12167,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12187,29 +12187,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
+          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>鸿蒙智行尚界用户中心•惠州惠博大道</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>鸿蒙智行尚界用户中心•惠州惠博大道</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12219,29 +12219,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
+          <t>广东省惠州市江北西区7号小区D1（金山汽车城内） → 广东省惠州市惠城区惠博大道江北西部7号小区金山汽车城3街1号B展场</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12251,29 +12251,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业） → 广西壮族自治区南宁市兴宁区三塘镇兴工北路汽车市场17-27号（临时营业）</t>
+          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12283,29 +12283,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
+          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12315,7 +12315,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
+          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
         </is>
       </c>
     </row>
@@ -12327,17 +12327,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•梅州梅塘东路</t>
+          <t>AITO授权用户中心•贵阳华通汽车城</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•梅州梅塘东路</t>
+          <t>AITO授权用户中心•贵阳华通汽车城</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12347,29 +12347,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>广东省梅州市梅江区梅塘东路30号 → 广东省梅州市梅江区三角镇梅塘东路30号</t>
+          <t>贵州省贵阳市云岩区金阳南路118号华通汽车城（临时营业） → 贵州省贵阳市云岩区金阳南路118号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12379,14 +12379,14 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•惠州惠博大道</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•惠州惠博大道</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12411,29 +12411,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>广东省惠州市江北西区7号小区D1（金山汽车城内） → 广东省惠州市惠城区惠博大道江北西部7号小区金山汽车城3街1号B展场</t>
+          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳华通汽车城</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳华通汽车城</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12443,29 +12443,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>贵州省贵阳市云岩区金阳南路118号华通汽车城（临时营业） → 贵州省贵阳市云岩区金阳南路118号</t>
+          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12475,29 +12475,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
+          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>鸿蒙智行尚界用户中心•梅州梅塘东路</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>鸿蒙智行尚界用户中心•梅州梅塘东路</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12507,7 +12507,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
+          <t>广东省梅州市梅江区梅塘东路30号 → 广东省梅州市梅江区三角镇梅塘东路30号</t>
         </is>
       </c>
     </row>
@@ -12738,22 +12738,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海松江区松江印象城</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市松江区松江印象城汽车体验店</t>
+          <t>小鹏汽车周口南环服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -12763,29 +12763,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 77%</t>
+          <t>店名相似度 88%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小米汽车上海松江区松江印象城</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环服务中心</t>
+          <t>小米之家上海市松江区松江印象城汽车体验店</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -12795,7 +12795,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 88%</t>
+          <t>店名相似度 77%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="新增网点（32家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="减少网点（28家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="变更明细（30条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（30家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（27家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（30条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -515,10 +515,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0</v>
@@ -662,17 +662,17 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
     </row>
@@ -683,10 +683,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>-4</v>
@@ -872,13 +872,13 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>8628</v>
+        <v>8632</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>8632</v>
+        <v>8635</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>0</v>
@@ -4663,10 +4663,10 @@
         </is>
       </c>
       <c r="C179" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D179" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E179" s="2" t="n">
         <v>0</v>
@@ -5016,14 +5016,14 @@
       </c>
       <c r="B196" s="4" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C196" s="4" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="D196" s="4" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="E196" s="4" t="n">
         <v>1</v>
@@ -5037,17 +5037,17 @@
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C197" s="4" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="D197" s="4" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="E197" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198">
@@ -5121,38 +5121,38 @@
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C201" s="3" t="n">
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="D201" s="3" t="n">
-        <v>34</v>
+        <v>83</v>
       </c>
       <c r="E201" s="3" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="3" t="inlineStr">
+      <c r="A202" s="2" t="inlineStr">
         <is>
           <t>小鹏</t>
         </is>
       </c>
-      <c r="B202" s="3" t="inlineStr">
-        <is>
-          <t>浙江</t>
-        </is>
-      </c>
-      <c r="C202" s="3" t="n">
-        <v>84</v>
-      </c>
-      <c r="D202" s="3" t="n">
-        <v>83</v>
-      </c>
-      <c r="E202" s="3" t="n">
-        <v>-1</v>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="D202" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E202" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="203">
@@ -5163,14 +5163,14 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C203" s="2" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="D203" s="2" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E203" s="2" t="n">
         <v>0</v>
@@ -5184,14 +5184,14 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C204" s="2" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="D204" s="2" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E204" s="2" t="n">
         <v>0</v>
@@ -5205,14 +5205,14 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C205" s="2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="D205" s="2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E205" s="2" t="n">
         <v>0</v>
@@ -5226,14 +5226,14 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C206" s="2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="D206" s="2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E206" s="2" t="n">
         <v>0</v>
@@ -5247,14 +5247,14 @@
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C207" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D207" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E207" s="2" t="n">
         <v>0</v>
@@ -5268,14 +5268,14 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C208" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D208" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E208" s="2" t="n">
         <v>0</v>
@@ -5289,14 +5289,14 @@
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C209" s="2" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="D209" s="2" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="E209" s="2" t="n">
         <v>0</v>
@@ -5310,14 +5310,14 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C210" s="2" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D210" s="2" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="E210" s="2" t="n">
         <v>0</v>
@@ -5331,14 +5331,14 @@
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C211" s="2" t="n">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="D211" s="2" t="n">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="E211" s="2" t="n">
         <v>0</v>
@@ -5352,14 +5352,14 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C212" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D212" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E212" s="2" t="n">
         <v>0</v>
@@ -5373,14 +5373,14 @@
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C213" s="2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D213" s="2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E213" s="2" t="n">
         <v>0</v>
@@ -5436,14 +5436,14 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C216" s="2" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="D216" s="2" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="E216" s="2" t="n">
         <v>0</v>
@@ -5457,14 +5457,14 @@
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C217" s="2" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D217" s="2" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="E217" s="2" t="n">
         <v>0</v>
@@ -5478,14 +5478,14 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C218" s="2" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="D218" s="2" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="E218" s="2" t="n">
         <v>0</v>
@@ -5499,14 +5499,14 @@
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C219" s="2" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="D219" s="2" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="E219" s="2" t="n">
         <v>0</v>
@@ -5520,14 +5520,14 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C220" s="2" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D220" s="2" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E220" s="2" t="n">
         <v>0</v>
@@ -5541,14 +5541,14 @@
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C221" s="2" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D221" s="2" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E221" s="2" t="n">
         <v>0</v>
@@ -5562,14 +5562,14 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C222" s="2" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D222" s="2" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="E222" s="2" t="n">
         <v>0</v>
@@ -5583,14 +5583,14 @@
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C223" s="2" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D223" s="2" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E223" s="2" t="n">
         <v>0</v>
@@ -5604,14 +5604,14 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C224" s="2" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D224" s="2" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="E224" s="2" t="n">
         <v>0</v>
@@ -5625,38 +5625,38 @@
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D225" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E225" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>小鹏</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C225" s="2" t="n">
+      <c r="C226" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D225" s="2" t="n">
+      <c r="D226" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E225" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" s="4" t="inlineStr">
-        <is>
-          <t>小鹏</t>
-        </is>
-      </c>
-      <c r="B226" s="4" t="inlineStr">
-        <is>
-          <t>新疆</t>
-        </is>
-      </c>
-      <c r="C226" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="D226" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E226" s="4" t="n">
-        <v>1</v>
+      <c r="E226" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="227">
@@ -10080,7 +10080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10088,6 +10088,7 @@
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10116,6 +10117,11 @@
           <t>地址</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>历史状态</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -10143,6 +10149,11 @@
           <t>云南省玉溪市红塔区棋阳路66号玉溪万达广场1F中庭</t>
         </is>
       </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -10170,6 +10181,11 @@
           <t>四川省成都市双流区天府新区中央商务区兴康三街505号天府大悦城北岛中庭</t>
         </is>
       </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -10197,6 +10213,11 @@
           <t>创业街1号</t>
         </is>
       </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -10206,7 +10227,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>小米汽车湖北省宜昌市宜都市宜都万达</t>
+          <t>小米汽车湖北省恩施市恩施和润城</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -10216,12 +10237,17 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>宜昌市</t>
+          <t>恩施土家族苗族自治州</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>湖北省宜昌市宜都市陆城宜华大道102号宜都万达1F中庭</t>
+          <t>湖北省恩施土家族苗族自治州恩施市和润城A馆中庭</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10233,34 +10259,39 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>小米汽车湖北省恩施市恩施和润城</t>
+          <t>小米汽车湖南省长沙市芙蓉区长沙芙蓉天街</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>恩施土家族苗族自治州</t>
+          <t>长沙市</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>湖北省恩施土家族苗族自治州恩施市和润城A馆中庭</t>
+          <t>湖南省长沙市芙蓉区人民东路与望龙路交汇处龙湖芙蓉天街1号门</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市芙蓉区长沙芙蓉天街</t>
+          <t>小鹏汽车常德湘西北汽车城销售中心</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -10270,93 +10301,113 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>长沙市</t>
+          <t>常德市</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>湖南省长沙市芙蓉区人民东路与望龙路交汇处龙湖芙蓉天街1号门</t>
+          <t>湖南省常德市武陵区常德大道湘西北汽车城内(龙港北路1088号)</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车昌吉市汽车城销售展厅</t>
+          <t>南昌沃瑞卫星店</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>昌吉回族自治州</t>
+          <t>南昌市</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区昌吉市北五路智慧新能源汽车城</t>
+          <t>江西省南昌市经济技术开发区玉屏东大街780号</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售中心</t>
+          <t>深圳福田卓悦中心体验店L123</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>常德市</t>
+          <t>深圳市</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区常德大道湘西北汽车城内(龙港北路1088号)</t>
+          <t>广东省深圳市福田区福华路与岗厦二路交叉口卓悦中心</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>南昌沃瑞卫星店</t>
+          <t>茂名茂悦东荟城城市展厅L1-1292</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>南昌市</t>
+          <t>茂名市</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>江西省南昌市经济技术开发区玉屏东大街780号</t>
+          <t>广东省茂名市茂南区油城十路与茂名大道交汇处东汇城L1层1292-293、1294-2商铺</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10368,22 +10419,27 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心体验店L123</t>
+          <t>库尔勒汇嘉时代</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>深圳市</t>
+          <t>巴音郭楞蒙古自治州</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>广东省深圳市福田区福华路与岗厦二路交叉口卓悦中心</t>
+          <t>新疆维吾尔自治区巴音郭楞蒙古自治州团结辖区朝阳路9库尔勒汇嘉号时代购物中心一楼DJL1006/DJL1007</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10395,157 +10451,187 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>茂名茂悦东荟城城市展厅L1-1292</t>
+          <t>莆田城厢万达广场</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>茂名市</t>
+          <t>莆田市</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>广东省茂名市茂南区油城十路与茂名大道交汇处东汇城L1层1292-293、1294-2商铺</t>
+          <t>福建省莆田市城厢区荔华东大道8号万达广场F1YX-ZT-002号展位</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>库尔勒汇嘉时代</t>
+          <t>理想汽车芜湖祥盛路零售中心</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>巴音郭楞蒙古自治州</t>
+          <t>芜湖市</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区巴音郭楞蒙古自治州团结辖区朝阳路9库尔勒汇嘉号时代购物中心一楼DJL1006/DJL1007</t>
+          <t>安徽省芜湖市鸠兹家苑汽车园祥盛路57号</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>莆田城厢万达广场</t>
+          <t>理想汽车江门蓬江临时交付中心</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>莆田市</t>
+          <t>江门市</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>福建省莆田市城厢区荔华东大道8号万达广场F1YX-ZT-002号展位</t>
+          <t>江门市蓬江区建设三路54号</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>阿斯顿·马丁</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>理想汽车芜湖祥盛路零售中心</t>
+          <t>阿斯顿·马丁苏州</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>芜湖市</t>
+          <t>苏州市</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>安徽省芜湖市鸠兹家苑汽车园祥盛路57号</t>
+          <t>苏州工业园区苏州大道东418号L101, 江苏省苏州市, 125127</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>理想汽车江门蓬江临时交付中心</t>
+          <t>华为授权体验店（宜家荟聚）</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>江门市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>江门市蓬江区建设三路54号</t>
+          <t>上海市长宁区金钟路788号01C04A 华为</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260504~20260615，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁苏州</t>
+          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>苏州市</t>
+          <t>鄂尔多斯市</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>苏州工业园区苏州大道东418号L101, 江苏省苏州市, 125127</t>
+          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260504~20260706，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10557,22 +10643,27 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（宜家荟聚）</t>
+          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>眉山市</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>上海市长宁区金钟路788号01C04A 华为</t>
+          <t>四川省眉山市东坡区眉州大道西五段99号1-2层</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260601~20260706，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10584,22 +10675,27 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
+          <t>AITO授权用户中心•天津西青大寺汽车园</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>鄂尔多斯市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼</t>
+          <t>天津市西青区大寺镇储源道17号</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260504~20260615，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10611,22 +10707,27 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
+          <t>鸿蒙智行授权用户中心•固原九龙路</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>眉山市</t>
+          <t>固原市</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>四川省眉山市东坡区眉州大道西五段99号1-2层</t>
+          <t>宁夏回族自治区固原市原州区九龙路与民族街交叉口</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10638,22 +10739,27 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•天津西青大寺汽车园</t>
+          <t>华为授权体验店（八佰伴）</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>芜湖市</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>天津市西青区大寺镇储源道17号</t>
+          <t>安徽省芜湖市镜湖区银湖路八佰伴生活广场3号门一楼华为授权体验店</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260504~20260706，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10665,22 +10771,27 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•固原九龙路</t>
+          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>固原市</t>
+          <t>芜湖市</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>宁夏回族自治区固原市原州区九龙路与民族街交叉口</t>
+          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260504~20260706，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10692,22 +10803,27 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（八佰伴）</t>
+          <t>鸿蒙智行授权用户中心•滨州渤海五路</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>芜湖市</t>
+          <t>滨州市</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>安徽省芜湖市镜湖区银湖路八佰伴生活广场3号门一楼华为授权体验店</t>
+          <t>山东省滨州市滨城区黄河十五路渤海五路北200米路东</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260504~20260706，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10719,22 +10835,27 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
+          <t>华为智能生活馆•烟台芝罘万达</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>芜湖市</t>
+          <t>烟台市</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口</t>
+          <t>山东省烟台市芝罘区西关南街万达广场一楼华为智能生活馆</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260504~20260615，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10746,22 +10867,27 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•滨州渤海五路</t>
+          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>滨州市</t>
+          <t>肇庆市</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>山东省滨州市滨城区黄河十五路渤海五路北200米路东</t>
+          <t>广东省肇庆市肇庆大道美轮车城北区2号楼</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260504~20260706，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10773,22 +10899,27 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•烟台芝罘万达</t>
+          <t>华为智能生活馆•无锡八佰伴中心</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>烟台市</t>
+          <t>无锡市</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>山东省烟台市芝罘区西关南街万达广场一楼华为智能生活馆</t>
+          <t>江苏省无锡市锡山区无锡八佰伴中心1F华为智能生活馆</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260504~20260615，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10800,22 +10931,27 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
+          <t>华为智能生活馆•郑州华联商厦</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>肇庆市</t>
+          <t>郑州市</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>广东省肇庆市肇庆大道美轮车城北区2号楼</t>
+          <t>河南省郑州市二七区二七路230号郑州华联商厦一层</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10827,22 +10963,27 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•无锡八佰伴中心</t>
+          <t>华为智能生活馆•嘉兴平湖吾悦</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>无锡市</t>
+          <t>嘉兴市</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>江苏省无锡市锡山区无锡八佰伴中心1F华为智能生活馆</t>
+          <t>浙江省嘉兴市平湖市当湖街道南市路811号吾悦广场1幢1楼1038-1商铺（内街）华为智能生活馆</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260504~20260615，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10854,22 +10995,27 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•郑州华联商厦</t>
+          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>郑州市</t>
+          <t>邵阳市</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>河南省郑州市二七区二七路230号郑州华联商厦一层</t>
+          <t>湖南省邵阳市双清区邵阳大道东联接线交叉口天骄汽配城内东100米</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260504~20260706，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10881,22 +11027,27 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•嘉兴平湖吾悦</t>
+          <t>鸿蒙智行授权用户中心•遵义汇川</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>嘉兴市</t>
+          <t>遵义市</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市平湖市当湖街道南市路811号吾悦广场1幢1楼1038-1商铺（内街）华为智能生活馆</t>
+          <t>贵州省遵义市汇川区董公寺街道和平社区汽车商贸城通源汽车文化广场内（临时营业）</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260504~20260615，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10908,76 +11059,27 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
+          <t>华为智能生活馆•重庆都市起点购物公园</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>邵阳市</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>湖南省邵阳市双清区邵阳大道东联接线交叉口天骄汽配城内东100米</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•遵义汇川</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>贵州</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>遵义市</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>贵州省遵义市汇川区董公寺街道和平社区汽车商贸城通源汽车文化广场内（临时营业）</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>华为智能生活馆•重庆都市起点购物公园</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>重庆</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
           <t>重庆市涪陵区兴华中路25号泽胜商业步行街都市起点购物公园L1层12/13/14号</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10992,7 +11094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11000,6 +11102,7 @@
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11028,6 +11131,11 @@
           <t>地址</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>历史状态</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -11055,6 +11163,11 @@
           <t>甘肃省兰州市城关区焦家湾南路105号</t>
         </is>
       </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -11082,6 +11195,11 @@
           <t>甘肃省天水市麦积区二十里铺街17号</t>
         </is>
       </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 11 期</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -11109,6 +11227,11 @@
           <t>陕西省安康市高新技术产业开发区钻石西路3号</t>
         </is>
       </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 11 期</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -11136,6 +11259,11 @@
           <t>上海虹口区西江湾路388号1F小米</t>
         </is>
       </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 11 期</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -11163,6 +11291,11 @@
           <t>民安大道2815-5号</t>
         </is>
       </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 11 期</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -11190,6 +11323,11 @@
           <t>东方爱琴海A馆1号门中庭</t>
         </is>
       </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 11 期</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -11217,6 +11355,11 @@
           <t>内江市经济技术开发区甜城大道中段347号</t>
         </is>
       </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 11 期</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -11226,7 +11369,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙华锦绣科学园服务中心</t>
+          <t>小鹏汽车深圳坂田环城南路服务中心</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -11241,7 +11384,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>广东省深圳市龙华区观湖街道松轩社区虎地排126号锦绣二期4号楼B4层01-26号铺</t>
+          <t>深圳市龙岗区坂田街道环城南路9号高力特智慧能源产业园</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 11 期</t>
         </is>
       </c>
     </row>
@@ -11253,7 +11401,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田环城南路服务中心</t>
+          <t>小鹏汽车深圳龙华锦绣科学园服务中心</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -11268,7 +11416,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>深圳市龙岗区坂田街道环城南路9号高力特智慧能源产业园</t>
+          <t>广东省深圳市龙华区观湖街道松轩社区虎地排126号锦绣二期4号楼B4层01-26号铺</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 11 期</t>
         </is>
       </c>
     </row>
@@ -11298,6 +11451,11 @@
           <t>江苏省南京市鼓楼区清凉门大街1号中海环宇城</t>
         </is>
       </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 11 期</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -11307,49 +11465,59 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车宁波印象城销售中心</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>洛阳市</t>
+          <t>宁波市</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园</t>
+          <t>浙江省宁波市鄞州区钱湖北街（路）288号 印象城F1层01-15商铺</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 11 期</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波印象城销售中心</t>
+          <t>武汉建银富瑞维修中心</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>宁波市</t>
+          <t>武汉市</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>浙江省宁波市鄞州区钱湖北街（路）288号 印象城F1层01-15商铺</t>
+          <t>湖北省武汉市洪山区和平乡铁机村2号铁机汽车展销中心A1-A4</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -11361,22 +11529,27 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>武汉建银富瑞维修中心</t>
+          <t>福州建发捷路4S中心</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>武汉市</t>
+          <t>福州市</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>湖北省武汉市洪山区和平乡铁机村2号铁机汽车展销中心A1-A4</t>
+          <t>福建省福州市马尾区马尾镇马江路28号</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 11 期</t>
         </is>
       </c>
     </row>
@@ -11388,7 +11561,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>福州建发捷路4S中心</t>
+          <t>福州建发众驰4S中心</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -11403,34 +11576,44 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市马尾区马尾镇马江路28号</t>
+          <t>福建省福州市闽侯县上街镇源通东路63号</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 11 期</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>福州建发众驰4S中心</t>
+          <t>深圳坪山益田假日广场</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>福州市</t>
+          <t>深圳市</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县上街镇源通东路63号</t>
+          <t>广东省深圳市坪山区坪山街道六联社区深汕路（坪山段）168号益田假日世界中庭CT-L1-05号</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 11 期</t>
         </is>
       </c>
     </row>
@@ -11442,49 +11625,59 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>深圳坪山益田假日广场</t>
+          <t>南昌红谷滩万达广场体验店</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>深圳市</t>
+          <t>南昌市</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>广东省深圳市坪山区坪山街道六联社区深汕路（坪山段）168号益田假日世界中庭CT-L1-05号</t>
+          <t>江西省南昌市红谷滩新区会展路999号万达广场</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 11 期</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>南昌红谷滩万达广场体验店</t>
+          <t>理想汽车银川悠阅城零售中心</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>南昌市</t>
+          <t>银川市</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>江西省南昌市红谷滩新区会展路999号万达广场</t>
+          <t>宁夏回族自治区银川市金凤区正源南街与凤仪路交会处悠阅城1号楼1层128号商铺</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 11 期</t>
         </is>
       </c>
     </row>
@@ -11496,22 +11689,27 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>理想汽车银川悠阅城零售中心</t>
+          <t>理想汽车东莞长安万达零售中心</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>银川市</t>
+          <t>东莞市</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>宁夏回族自治区银川市金凤区正源南街与凤仪路交会处悠阅城1号楼1层128号商铺</t>
+          <t>广东省东莞市长安镇霄边社区东门中路1号长安万达广场2号门1007室</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 11 期</t>
         </is>
       </c>
     </row>
@@ -11523,22 +11721,27 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>理想汽车东莞长安万达零售中心</t>
+          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>东莞市</t>
+          <t>伊犁</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>广东省东莞市长安镇霄边社区东门中路1号长安万达广场2号门1007室</t>
+          <t>新疆伊犁哈萨克自治州伊宁市巴彦岱镇三段村资源路1号伊宁城投汽车产业园一号展厅东侧二楼202室</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 8 期</t>
         </is>
       </c>
     </row>
@@ -11550,22 +11753,27 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
+          <t>理想汽车毕节双山国际汽车城授权钣喷中心（荣信店）</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>伊犁</t>
+          <t>毕节市</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>新疆伊犁哈萨克自治州伊宁市巴彦岱镇三段村资源路1号伊宁城投汽车产业园一号展厅东侧二楼202室</t>
+          <t>贵州省毕节市七星关区响水乡吊兰社区小瓦路8号双山国际汽车城1-1号商铺</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 11 期</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11785,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>理想汽车毕节双山国际汽车城授权钣喷中心（荣信店）</t>
+          <t>理想汽车贵阳花溪临时交付中心</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -11587,12 +11795,17 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>毕节市</t>
+          <t>贵阳市</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>贵州省毕节市七星关区响水乡吊兰社区小瓦路8号双山国际汽车城1-1号商铺</t>
+          <t>贵阳市花溪区孟关乡孟关村 A-22</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 11 期</t>
         </is>
       </c>
     </row>
@@ -11604,49 +11817,59 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>理想汽车贵阳花溪临时交付中心</t>
+          <t>理想汽车大连华南万象汇零售中心</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>贵阳市</t>
+          <t>大连市</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>贵阳市花溪区孟关乡孟关村 A-22</t>
+          <t>辽宁省大连市甘井子区山东路 350 号、352 号 华润置地 大连华南万象汇 的 LG203</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 11 期</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>阿斯顿·马丁</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>理想汽车大连华南万象汇零售中心</t>
+          <t>阿斯顿·马丁北京售后服务中心</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>大连市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>辽宁省大连市甘井子区山东路 350 号、352 号 华润置地 大连华南万象汇 的 LG203</t>
+          <t>大兴区金时大街7号院5号楼, 北京, 100076</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 11 期</t>
         </is>
       </c>
     </row>
@@ -11658,7 +11881,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁北京售后服务中心</t>
+          <t>阿斯顿·马丁北京</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -11673,34 +11896,44 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>大兴区金时大街7号院5号楼, 北京, 100076</t>
+          <t>东城区金宝街99号 , 北京, 100005</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 11 期</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁北京</t>
+          <t>鸿蒙智行尚界用户中心•运城机场大道</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>运城市</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>东城区金宝街99号 , 北京, 100005</t>
+          <t>山西省运城市盐湖区机场大道与库东路交叉口西南160米</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 11 期</t>
         </is>
       </c>
     </row>
@@ -11712,22 +11945,27 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•运城机场大道</t>
+          <t>华为智能生活馆•邢台逗号立方</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>运城市</t>
+          <t>邢台市</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>山西省运城市盐湖区机场大道与库东路交叉口西南160米</t>
+          <t>河北省邢台市信都区中兴西大街逗号立方购物公园1F</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 11 期</t>
         </is>
       </c>
     </row>
@@ -11739,49 +11977,27 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•邢台逗号立方</t>
+          <t>华为智能生活馆•武汉经开永旺梦乐城</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>邢台市</t>
+          <t>武汉市</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>河北省邢台市信都区中兴西大街逗号立方购物公园1F</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>华为智能生活馆•武汉经开永旺梦乐城</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>湖北</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>武汉市</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
           <t>武汉经济技术开发区江城大道永旺梦乐城NO.B113b</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 11 期</t>
         </is>
       </c>
     </row>
@@ -11842,22 +12058,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•余慈鑫时代</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•余慈鑫时代</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11867,29 +12083,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>慈溪市横河镇前应路1176号 → 浙江省慈溪市横河镇前应路1176号</t>
+          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11899,29 +12115,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
+          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11931,29 +12147,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
+          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•嘉兴南溪东路</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•嘉兴南溪东路</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11963,29 +12179,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区大桥镇南溪东路1362号0003幢（临时营业） → 浙江省嘉兴市南湖区南溪东路1362号</t>
+          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>鸿蒙智行尚界用户中心•嘉兴南溪东路</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>鸿蒙智行尚界用户中心•嘉兴南溪东路</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11995,7 +12211,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
+          <t>浙江省嘉兴市南湖区大桥镇南溪东路1362号0003幢（临时营业） → 浙江省嘉兴市南湖区南溪东路1362号</t>
         </is>
       </c>
     </row>
@@ -12007,17 +12223,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>鸿蒙智行尚界用户中心•惠州惠博大道</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>鸿蒙智行尚界用户中心•惠州惠博大道</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12027,7 +12243,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业） → 广西壮族自治区南宁市兴宁区三塘镇兴工北路汽车市场17-27号（临时营业）</t>
+          <t>广东省惠州市江北西区7号小区D1（金山汽车城内） → 广东省惠州市惠城区惠博大道江北西部7号小区金山汽车城3街1号B展场</t>
         </is>
       </c>
     </row>
@@ -12039,17 +12255,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12059,29 +12275,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
+          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12091,29 +12307,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12123,29 +12339,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
+          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•梅州梅塘东路</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•梅州梅塘东路</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12155,29 +12371,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
+          <t>广东省梅州市梅江区梅塘东路30号 → 广东省梅州市梅江区三角镇梅塘东路30号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12187,29 +12403,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
+          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•惠州惠博大道</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•惠州惠博大道</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12219,29 +12435,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>广东省惠州市江北西区7号小区D1（金山汽车城内） → 广东省惠州市惠城区惠博大道江北西部7号小区金山汽车城3街1号B展场</t>
+          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>AITO授权用户中心•余慈鑫时代</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>AITO授权用户中心•余慈鑫时代</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12251,29 +12467,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
+          <t>慈溪市横河镇前应路1176号 → 浙江省慈溪市横河镇前应路1176号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12283,14 +12499,14 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
+          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -12300,12 +12516,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12315,29 +12531,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
+          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳华通汽车城</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳华通汽车城</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12347,29 +12563,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>贵州省贵阳市云岩区金阳南路118号华通汽车城（临时营业） → 贵州省贵阳市云岩区金阳南路118号</t>
+          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>AITO授权用户中心•贵阳华通汽车城</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>AITO授权用户中心•贵阳华通汽车城</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12379,29 +12595,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>贵州省贵阳市云岩区金阳南路118号华通汽车城（临时营业） → 贵州省贵阳市云岩区金阳南路118号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12411,29 +12627,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
+          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12443,7 +12659,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
+          <t>广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业） → 广西壮族自治区南宁市兴宁区三塘镇兴工北路汽车市场17-27号（临时营业）</t>
         </is>
       </c>
     </row>
@@ -12455,17 +12671,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12475,29 +12691,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
+          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•梅州梅塘东路</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•梅州梅塘东路</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12507,7 +12723,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>广东省梅州市梅江区梅塘东路30号 → 广东省梅州市梅江区三角镇梅塘东路30号</t>
+          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
         </is>
       </c>
     </row>
@@ -12546,22 +12762,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>理想汽车铜仁万山授权钣喷中心（俊汇店）</t>
+          <t>鸿蒙智行尚界用户中心•三明北汽车城</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>理想汽车铜仁万山授权服务中心（俊汇店）</t>
+          <t>鸿蒙智行授权用户中心•三明北汽车城</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -12578,22 +12794,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鹿城零售中心</t>
+          <t>天津鲁能城城市中心店</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州鹿城零售中心</t>
+          <t>天津贵和城市中心店</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -12610,22 +12826,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>奔驰</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>天津鲁能城城市中心店</t>
+          <t>宜春华宏臻汽车有限公司</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>天津贵和城市中心店</t>
+          <t>宜春华宏星汽车有限公司</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -12642,22 +12858,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•三明北汽车城</t>
+          <t>理想汽车铜仁万山授权钣喷中心（俊汇店）</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•三明北汽车城</t>
+          <t>理想汽车铜仁万山授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -12674,22 +12890,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>奔驰</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>宜春华宏臻汽车有限公司</t>
+          <t>理想汽车鹿城零售中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>宜春华宏星汽车有限公司</t>
+          <t>理想汽车温州鹿城零售中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -12738,22 +12954,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小米汽车上海松江区松江印象城</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环服务中心</t>
+          <t>小米之家上海市松江区松江印象城汽车体验店</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -12763,29 +12979,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 88%</t>
+          <t>店名相似度 77%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海松江区松江印象城</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市松江区松江印象城汽车体验店</t>
+          <t>小鹏汽车周口南环服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -12795,7 +13011,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 77%</t>
+          <t>店名相似度 88%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
@@ -11102,7 +11102,7 @@
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>连续在档 11 期</t>
+          <t>连续在档 11 期；本期存在高相似店名「理想汽车银川建发阅彩城零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -11709,7 +11709,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>连续在档 11 期</t>
+          <t>连续在档 11 期；本期存在高相似店名「理想汽车东莞东城万达零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -11933,7 +11933,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>连续在档 11 期</t>
+          <t>连续在档 11 期；本期存在高相似店名「鸿蒙智行授权用户中心•运城机场大道」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -11965,7 +11965,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>连续在档 11 期</t>
+          <t>连续在档 11 期；本期同名店仍在档（地址写法变更，非关店）</t>
         </is>
       </c>
     </row>
@@ -12058,7 +12058,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12083,29 +12083,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
+          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•惠州惠博大道</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•惠州惠博大道</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12115,29 +12115,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
+          <t>广东省惠州市江北西区7号小区D1（金山汽车城内） → 广东省惠州市惠城区惠博大道江北西部7号小区金山汽车城3街1号B展场</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
+          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
         </is>
       </c>
     </row>
@@ -12159,17 +12159,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12179,29 +12179,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
+          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•嘉兴南溪东路</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•嘉兴南溪东路</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12211,29 +12211,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区大桥镇南溪东路1362号0003幢（临时营业） → 浙江省嘉兴市南湖区南溪东路1362号</t>
+          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•惠州惠博大道</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•惠州惠博大道</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12243,29 +12243,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>广东省惠州市江北西区7号小区D1（金山汽车城内） → 广东省惠州市惠城区惠博大道江北西部7号小区金山汽车城3街1号B展场</t>
+          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>AITO授权用户中心•余慈鑫时代</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>AITO授权用户中心•余慈鑫时代</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
+          <t>慈溪市横河镇前应路1176号 → 浙江省慈溪市横河镇前应路1176号</t>
         </is>
       </c>
     </row>
@@ -12287,17 +12287,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12307,7 +12307,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
         </is>
       </c>
     </row>
@@ -12319,17 +12319,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12339,29 +12339,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
+          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•梅州梅塘东路</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•梅州梅塘东路</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12371,29 +12371,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>广东省梅州市梅江区梅塘东路30号 → 广东省梅州市梅江区三角镇梅塘东路30号</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•嘉兴南溪东路</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•嘉兴南溪东路</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12403,29 +12403,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
+          <t>浙江省嘉兴市南湖区大桥镇南溪东路1362号0003幢（临时营业） → 浙江省嘉兴市南湖区南溪东路1362号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12435,29 +12435,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
+          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•余慈鑫时代</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•余慈鑫时代</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12467,29 +12467,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>慈溪市横河镇前应路1176号 → 浙江省慈溪市横河镇前应路1176号</t>
+          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>鸿蒙智行尚界用户中心•梅州梅塘东路</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>鸿蒙智行尚界用户中心•梅州梅塘东路</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12499,7 +12499,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
+          <t>广东省梅州市梅江区梅塘东路30号 → 广东省梅州市梅江区三角镇梅塘东路30号</t>
         </is>
       </c>
     </row>
@@ -12575,17 +12575,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳华通汽车城</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳华通汽车城</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12595,29 +12595,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>贵州省贵阳市云岩区金阳南路118号华通汽车城（临时营业） → 贵州省贵阳市云岩区金阳南路118号</t>
+          <t>广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业） → 广西壮族自治区南宁市兴宁区三塘镇兴工北路汽车市场17-27号（临时营业）</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12627,29 +12627,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
+          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12659,7 +12659,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业） → 广西壮族自治区南宁市兴宁区三塘镇兴工北路汽车市场17-27号（临时营业）</t>
+          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
         </is>
       </c>
     </row>
@@ -12671,17 +12671,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12691,29 +12691,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
+          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>AITO授权用户中心•贵阳华通汽车城</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>AITO授权用户中心•贵阳华通汽车城</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12723,7 +12723,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
+          <t>贵州省贵阳市云岩区金阳南路118号华通汽车城（临时营业） → 贵州省贵阳市云岩区金阳南路118号</t>
         </is>
       </c>
     </row>
@@ -12762,22 +12762,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•三明北汽车城</t>
+          <t>天津鲁能城城市中心店</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•三明北汽车城</t>
+          <t>天津贵和城市中心店</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -12794,22 +12794,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>天津鲁能城城市中心店</t>
+          <t>鸿蒙智行尚界用户中心•三明北汽车城</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>天津贵和城市中心店</t>
+          <t>鸿蒙智行授权用户中心•三明北汽车城</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -12954,22 +12954,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海松江区松江印象城</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市松江区松江印象城汽车体验店</t>
+          <t>小鹏汽车周口南环服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -12979,29 +12979,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 77%</t>
+          <t>店名相似度 88%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小米汽车上海松江区松江印象城</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环服务中心</t>
+          <t>小米之家上海市松江区松江印象城汽车体验店</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 88%</t>
+          <t>店名相似度 77%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
@@ -9,9 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（30家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（27家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（30条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（24家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（25家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（23条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -851,17 +851,17 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>1711</v>
+        <v>1451</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1724</v>
+        <v>1460</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.6%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>8632</v>
+        <v>8372</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>8635</v>
+        <v>8371</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-0.0%</t>
         </is>
       </c>
     </row>
@@ -9426,59 +9426,59 @@
       </c>
       <c r="B406" s="3" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C406" s="3" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="D406" s="3" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="E406" s="3" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="407">
-      <c r="A407" s="3" t="inlineStr">
+      <c r="A407" s="2" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B407" s="3" t="inlineStr">
-        <is>
-          <t>河北</t>
-        </is>
-      </c>
-      <c r="C407" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="D407" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="E407" s="3" t="n">
-        <v>-1</v>
+      <c r="B407" s="2" t="inlineStr">
+        <is>
+          <t>云南</t>
+        </is>
+      </c>
+      <c r="C407" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="D407" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="E407" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="408">
-      <c r="A408" s="3" t="inlineStr">
+      <c r="A408" s="2" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B408" s="3" t="inlineStr">
-        <is>
-          <t>湖北</t>
-        </is>
-      </c>
-      <c r="C408" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="D408" s="3" t="n">
-        <v>57</v>
-      </c>
-      <c r="E408" s="3" t="n">
-        <v>-1</v>
+      <c r="B408" s="2" t="inlineStr">
+        <is>
+          <t>内蒙古</t>
+        </is>
+      </c>
+      <c r="C408" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="D408" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="E408" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="409">
@@ -9489,14 +9489,14 @@
       </c>
       <c r="B409" s="2" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C409" s="2" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="D409" s="2" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E409" s="2" t="n">
         <v>0</v>
@@ -9510,14 +9510,14 @@
       </c>
       <c r="B410" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C410" s="2" t="n">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="D410" s="2" t="n">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="E410" s="2" t="n">
         <v>0</v>
@@ -9531,14 +9531,14 @@
       </c>
       <c r="B411" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C411" s="2" t="n">
-        <v>21</v>
+        <v>79</v>
       </c>
       <c r="D411" s="2" t="n">
-        <v>21</v>
+        <v>79</v>
       </c>
       <c r="E411" s="2" t="n">
         <v>0</v>
@@ -9552,14 +9552,14 @@
       </c>
       <c r="B412" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C412" s="2" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D412" s="2" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E412" s="2" t="n">
         <v>0</v>
@@ -9573,14 +9573,14 @@
       </c>
       <c r="B413" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C413" s="2" t="n">
-        <v>26</v>
+        <v>181</v>
       </c>
       <c r="D413" s="2" t="n">
-        <v>26</v>
+        <v>181</v>
       </c>
       <c r="E413" s="2" t="n">
         <v>0</v>
@@ -9594,14 +9594,14 @@
       </c>
       <c r="B414" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C414" s="2" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D414" s="2" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="E414" s="2" t="n">
         <v>0</v>
@@ -9615,14 +9615,14 @@
       </c>
       <c r="B415" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C415" s="2" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D415" s="2" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E415" s="2" t="n">
         <v>0</v>
@@ -9636,14 +9636,14 @@
       </c>
       <c r="B416" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C416" s="2" t="n">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="D416" s="2" t="n">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="E416" s="2" t="n">
         <v>0</v>
@@ -9657,14 +9657,14 @@
       </c>
       <c r="B417" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C417" s="2" t="n">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="D417" s="2" t="n">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="E417" s="2" t="n">
         <v>0</v>
@@ -9678,14 +9678,14 @@
       </c>
       <c r="B418" s="2" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C418" s="2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D418" s="2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E418" s="2" t="n">
         <v>0</v>
@@ -9699,14 +9699,14 @@
       </c>
       <c r="B419" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C419" s="2" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D419" s="2" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E419" s="2" t="n">
         <v>0</v>
@@ -9720,14 +9720,14 @@
       </c>
       <c r="B420" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C420" s="2" t="n">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="D420" s="2" t="n">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="E420" s="2" t="n">
         <v>0</v>
@@ -9741,14 +9741,14 @@
       </c>
       <c r="B421" s="2" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C421" s="2" t="n">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="D421" s="2" t="n">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="E421" s="2" t="n">
         <v>0</v>
@@ -9762,101 +9762,101 @@
       </c>
       <c r="B422" s="2" t="inlineStr">
         <is>
+          <t>西藏</t>
+        </is>
+      </c>
+      <c r="C422" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D422" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E422" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B423" s="2" t="inlineStr">
+        <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="C423" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="D423" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="E423" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B424" s="2" t="inlineStr">
+        <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C424" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="D424" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="E424" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B425" s="2" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C425" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D425" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E425" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B426" s="2" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C422" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="D422" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="E422" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="423">
-      <c r="A423" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B423" s="4" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C423" s="4" t="n">
-        <v>66</v>
-      </c>
-      <c r="D423" s="4" t="n">
-        <v>67</v>
-      </c>
-      <c r="E423" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="424">
-      <c r="A424" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B424" s="4" t="inlineStr">
-        <is>
-          <t>内蒙古</t>
-        </is>
-      </c>
-      <c r="C424" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="D424" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="E424" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="425">
-      <c r="A425" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B425" s="4" t="inlineStr">
-        <is>
-          <t>四川</t>
-        </is>
-      </c>
-      <c r="C425" s="4" t="n">
-        <v>92</v>
-      </c>
-      <c r="D425" s="4" t="n">
-        <v>93</v>
-      </c>
-      <c r="E425" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="426">
-      <c r="A426" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B426" s="4" t="inlineStr">
-        <is>
-          <t>天津</t>
-        </is>
-      </c>
-      <c r="C426" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="D426" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="E426" s="4" t="n">
-        <v>1</v>
+      <c r="C426" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="D426" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="E426" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="427">
@@ -9867,14 +9867,14 @@
       </c>
       <c r="B427" s="4" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C427" s="4" t="n">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="D427" s="4" t="n">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="E427" s="4" t="n">
         <v>1</v>
@@ -9888,14 +9888,14 @@
       </c>
       <c r="B428" s="4" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C428" s="4" t="n">
-        <v>205</v>
+        <v>19</v>
       </c>
       <c r="D428" s="4" t="n">
-        <v>206</v>
+        <v>20</v>
       </c>
       <c r="E428" s="4" t="n">
         <v>1</v>
@@ -9909,14 +9909,14 @@
       </c>
       <c r="B429" s="4" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C429" s="4" t="n">
-        <v>142</v>
+        <v>10</v>
       </c>
       <c r="D429" s="4" t="n">
-        <v>143</v>
+        <v>11</v>
       </c>
       <c r="E429" s="4" t="n">
         <v>1</v>
@@ -9930,14 +9930,14 @@
       </c>
       <c r="B430" s="4" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C430" s="4" t="n">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="D430" s="4" t="n">
-        <v>85</v>
+        <v>47</v>
       </c>
       <c r="E430" s="4" t="n">
         <v>1</v>
@@ -9951,14 +9951,14 @@
       </c>
       <c r="B431" s="4" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C431" s="4" t="n">
-        <v>151</v>
+        <v>79</v>
       </c>
       <c r="D431" s="4" t="n">
-        <v>152</v>
+        <v>80</v>
       </c>
       <c r="E431" s="4" t="n">
         <v>1</v>
@@ -9972,14 +9972,14 @@
       </c>
       <c r="B432" s="4" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C432" s="4" t="n">
-        <v>66</v>
+        <v>123</v>
       </c>
       <c r="D432" s="4" t="n">
-        <v>67</v>
+        <v>124</v>
       </c>
       <c r="E432" s="4" t="n">
         <v>1</v>
@@ -9993,14 +9993,14 @@
       </c>
       <c r="B433" s="4" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C433" s="4" t="n">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="D433" s="4" t="n">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="E433" s="4" t="n">
         <v>1</v>
@@ -10014,14 +10014,14 @@
       </c>
       <c r="B434" s="4" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C434" s="4" t="n">
-        <v>44</v>
+        <v>140</v>
       </c>
       <c r="D434" s="4" t="n">
-        <v>45</v>
+        <v>141</v>
       </c>
       <c r="E434" s="4" t="n">
         <v>1</v>
@@ -10035,17 +10035,17 @@
       </c>
       <c r="B435" s="4" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C435" s="4" t="n">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="D435" s="4" t="n">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="E435" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="436">
@@ -10056,17 +10056,17 @@
       </c>
       <c r="B436" s="4" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C436" s="4" t="n">
-        <v>104</v>
+        <v>37</v>
       </c>
       <c r="D436" s="4" t="n">
-        <v>106</v>
+        <v>38</v>
       </c>
       <c r="E436" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -10080,7 +10080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10611,27 +10611,27 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
+          <t>AITO授权用户中心•天津西青大寺汽车园</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>鄂尔多斯市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼</t>
+          <t>天津市西青区大寺镇储源道17号</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260706，疑似此前漏爬）</t>
+          <t>回归（曾出现 20260504~20260615，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10643,27 +10643,27 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
+          <t>鸿蒙智行授权用户中心•固原九龙路</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>眉山市</t>
+          <t>固原市</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>四川省眉山市东坡区眉州大道西五段99号1-2层</t>
+          <t>宁夏回族自治区固原市原州区九龙路与民族街交叉口</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260601~20260706，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10675,27 +10675,27 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•天津西青大寺汽车园</t>
+          <t>华为授权体验店（八佰伴）</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>芜湖市</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>天津市西青区大寺镇储源道17号</t>
+          <t>安徽省芜湖市镜湖区银湖路八佰伴生活广场3号门一楼华为授权体验店</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260615，疑似此前漏爬）</t>
+          <t>回归（曾出现 20260504~20260706，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10707,27 +10707,27 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•固原九龙路</t>
+          <t>华为智能生活馆•烟台芝罘万达</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>固原市</t>
+          <t>烟台市</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>宁夏回族自治区固原市原州区九龙路与民族街交叉口</t>
+          <t>山东省烟台市芝罘区西关南街万达广场一楼华为智能生活馆</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260615，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10739,27 +10739,27 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（八佰伴）</t>
+          <t>华为智能生活馆•无锡八佰伴中心</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>芜湖市</t>
+          <t>无锡市</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>安徽省芜湖市镜湖区银湖路八佰伴生活广场3号门一楼华为授权体验店</t>
+          <t>江苏省无锡市锡山区无锡八佰伴中心1F华为智能生活馆</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260706，疑似此前漏爬）</t>
+          <t>回归（曾出现 20260504~20260615，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10771,27 +10771,27 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
+          <t>华为智能生活馆•郑州华联商厦</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>芜湖市</t>
+          <t>郑州市</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口</t>
+          <t>河南省郑州市二七区二七路230号郑州华联商厦一层</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260706，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10803,27 +10803,27 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•滨州渤海五路</t>
+          <t>华为智能生活馆•嘉兴平湖吾悦</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>滨州市</t>
+          <t>嘉兴市</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>山东省滨州市滨城区黄河十五路渤海五路北200米路东</t>
+          <t>浙江省嘉兴市平湖市当湖街道南市路811号吾悦广场1幢1楼1038-1商铺（内街）华为智能生活馆</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260706，疑似此前漏爬）</t>
+          <t>回归（曾出现 20260504~20260615，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10835,22 +10835,22 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•烟台芝罘万达</t>
+          <t>鸿蒙智行授权用户中心•遵义汇川</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>烟台市</t>
+          <t>遵义市</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>山东省烟台市芝罘区西关南街万达广场一楼华为智能生活馆</t>
+          <t>贵州省遵义市汇川区董公寺街道和平社区汽车商贸城通源汽车文化广场内（临时营业）</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -10867,217 +10867,25 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
+          <t>华为智能生活馆•重庆都市起点购物公园</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>肇庆市</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>广东省肇庆市肇庆大道美轮车城北区2号楼</t>
+          <t>重庆市涪陵区兴华中路25号泽胜商业步行街都市起点购物公园L1层12/13/14号</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>回归（曾出现 20260504~20260706，疑似此前漏爬）</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>华为智能生活馆•无锡八佰伴中心</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>江苏</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>无锡市</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>江苏省无锡市锡山区无锡八佰伴中心1F华为智能生活馆</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>回归（曾出现 20260504~20260615，疑似此前漏爬）</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>华为智能生活馆•郑州华联商厦</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>河南</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>郑州市</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>河南省郑州市二七区二七路230号郑州华联商厦一层</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>全新</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>华为智能生活馆•嘉兴平湖吾悦</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>浙江</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>嘉兴市</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>浙江省嘉兴市平湖市当湖街道南市路811号吾悦广场1幢1楼1038-1商铺（内街）华为智能生活馆</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>回归（曾出现 20260504~20260615，疑似此前漏爬）</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>湖南</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>邵阳市</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>湖南省邵阳市双清区邵阳大道东联接线交叉口天骄汽配城内东100米</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>回归（曾出现 20260504~20260706，疑似此前漏爬）</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•遵义汇川</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>贵州</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>遵义市</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>贵州省遵义市汇川区董公寺街道和平社区汽车商贸城通源汽车文化广场内（临时营业）</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>回归（曾出现 20260504~20260615，疑似此前漏爬）</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>华为智能生活馆•重庆都市起点购物公园</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>重庆</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>重庆市涪陵区兴华中路25号泽胜商业步行街都市起点购物公园L1层12/13/14号</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
         <is>
           <t>全新</t>
         </is>
@@ -11094,7 +10902,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11529,7 +11337,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>福州建发捷路4S中心</t>
+          <t>福州建发众驰4S中心</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -11544,7 +11352,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市马尾区马尾镇马江路28号</t>
+          <t>福建省福州市闽侯县上街镇源通东路63号</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -11561,7 +11369,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>福州建发众驰4S中心</t>
+          <t>福州建发捷路4S中心</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -11576,7 +11384,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县上街镇源通东路63号</t>
+          <t>福建省福州市马尾区马尾镇马江路28号</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -11849,7 +11657,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁北京售后服务中心</t>
+          <t>阿斯顿·马丁北京</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11864,7 +11672,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>大兴区金时大街7号院5号楼, 北京, 100076</t>
+          <t>东城区金宝街99号 , 北京, 100005</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -11881,7 +11689,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁北京</t>
+          <t>阿斯顿·马丁北京售后服务中心</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -11896,7 +11704,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>东城区金宝街99号 , 北京, 100005</t>
+          <t>大兴区金时大街7号院5号楼, 北京, 100076</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -11913,89 +11721,25 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•运城机场大道</t>
+          <t>华为智能生活馆•武汉经开永旺梦乐城</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>运城市</t>
+          <t>武汉市</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>山西省运城市盐湖区机场大道与库东路交叉口西南160米</t>
+          <t>武汉经济技术开发区江城大道永旺梦乐城NO.B113b</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>连续在档 11 期；本期存在高相似店名「鸿蒙智行授权用户中心•运城机场大道」（疑似改名/合并，非真实关店）</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>华为智能生活馆•邢台逗号立方</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>河北</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>邢台市</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>河北省邢台市信都区中兴西大街逗号立方购物公园1F</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>连续在档 11 期；本期同名店仍在档（地址写法变更，非关店）</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>华为智能生活馆•武汉经开永旺梦乐城</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>湖北</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>武汉市</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>武汉经济技术开发区江城大道永旺梦乐城NO.B113b</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
         <is>
           <t>连续在档 11 期</t>
         </is>
@@ -12012,10 +11756,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
     <col width="27" customWidth="1" min="4" max="4"/>
@@ -12058,22 +11802,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12083,29 +11827,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
+          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•惠州惠博大道</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•惠州惠博大道</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12115,7 +11859,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>广东省惠州市江北西区7号小区D1（金山汽车城内） → 广东省惠州市惠城区惠博大道江北西部7号小区金山汽车城3街1号B展场</t>
+          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
         </is>
       </c>
     </row>
@@ -12154,22 +11898,22 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12179,7 +11923,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
+          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
         </is>
       </c>
     </row>
@@ -12191,17 +11935,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12211,29 +11955,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
+          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12243,29 +11987,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
+          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•余慈鑫时代</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•余慈鑫时代</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12275,7 +12019,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>慈溪市横河镇前应路1176号 → 浙江省慈溪市横河镇前应路1176号</t>
+          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
         </is>
       </c>
     </row>
@@ -12287,17 +12031,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12307,29 +12051,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
+          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12339,29 +12083,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
+          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12371,29 +12115,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•嘉兴南溪东路</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•嘉兴南溪东路</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12403,29 +12147,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区大桥镇南溪东路1362号0003幢（临时营业） → 浙江省嘉兴市南湖区南溪东路1362号</t>
+          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12435,7 +12179,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
+          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
         </is>
       </c>
     </row>
@@ -12447,17 +12191,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12467,29 +12211,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
+          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•梅州梅塘东路</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•梅州梅塘东路</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12499,7 +12243,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>广东省梅州市梅江区梅塘东路30号 → 广东省梅州市梅江区三角镇梅塘东路30号</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
@@ -12516,12 +12260,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12531,14 +12275,14 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
+          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -12548,44 +12292,44 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>小鹏汽车东莞松山湖服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>小鹏汽车东莞松山湖交付中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>地址变更</t>
+          <t>店名变更</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
+          <t>小鹏汽车东莞松山湖服务中心 → 小鹏汽车东莞松山湖交付中心</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奔驰</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>宜春华宏臻汽车有限公司</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>宜春华宏星汽车有限公司</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12595,29 +12339,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业） → 广西壮族自治区南宁市兴宁区三塘镇兴工北路汽车市场17-27号（临时营业）</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>理想汽车铜仁万山授权钣喷中心（俊汇店）</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>理想汽车铜仁万山授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12627,29 +12371,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>理想汽车鹿城零售中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>理想汽车温州鹿城零售中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12659,29 +12403,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>天津鲁能城城市中心店</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>天津贵和城市中心店</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12691,29 +12435,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳华通汽车城</t>
+          <t>宜宾万象天地城市展厅NL1-C-N-1</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳华通汽车城</t>
+          <t>宜宾万象天地城市展厅B01-C-N-1</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12723,7 +12467,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>贵州省贵阳市云岩区金阳南路118号华通汽车城（临时营业） → 贵州省贵阳市云岩区金阳南路118号</t>
+          <t>地址相似度 87%</t>
         </is>
       </c>
     </row>
@@ -12735,17 +12479,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东莞松山湖服务中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东莞松山湖交付中心</t>
+          <t>小鹏汽车周口南环服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12755,261 +12499,37 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东莞松山湖服务中心 → 小鹏汽车东莞松山湖交付中心</t>
+          <t>店名相似度 88%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>天津鲁能城城市中心店</t>
+          <t>小米汽车上海松江区松江印象城</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>天津贵和城市中心店</t>
+          <t>小米之家上海市松江区松江印象城汽车体验店</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>地址变更</t>
+          <t>店名变更</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>福建</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行尚界用户中心•三明北汽车城</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•三明北汽车城</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>奔驰</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>江西</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>宜春华宏臻汽车有限公司</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>宜春华宏星汽车有限公司</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>贵州</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>理想汽车铜仁万山授权钣喷中心（俊汇店）</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>理想汽车铜仁万山授权服务中心（俊汇店）</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>浙江</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>理想汽车鹿城零售中心</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>理想汽车温州鹿城零售中心</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>四川</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>宜宾万象天地城市展厅NL1-C-N-1</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>宜宾万象天地城市展厅B01-C-N-1</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>地址相似度 87%</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>小鹏</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>河南</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>小鹏汽车周口南环服务中心</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>店名变更</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>店名相似度 88%</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>小米</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>小米汽车上海松江区松江印象城</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>小米之家上海市松江区松江印象城汽车体验店</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>店名变更</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>店名相似度 77%</t>
         </is>

--- a/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
@@ -851,10 +851,10 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>9</v>
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>8372</v>
+        <v>8371</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>8371</v>
+        <v>8370</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>-1</v>
@@ -9766,10 +9766,10 @@
         </is>
       </c>
       <c r="C422" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D422" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E422" s="2" t="n">
         <v>0</v>
@@ -11177,7 +11177,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田环城南路服务中心</t>
+          <t>小鹏汽车深圳龙华锦绣科学园服务中心</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -11192,7 +11192,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>深圳市龙岗区坂田街道环城南路9号高力特智慧能源产业园</t>
+          <t>广东省深圳市龙华区观湖街道松轩社区虎地排126号锦绣二期4号楼B4层01-26号铺</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -11209,7 +11209,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙华锦绣科学园服务中心</t>
+          <t>小鹏汽车深圳坂田环城南路服务中心</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -11224,7 +11224,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>广东省深圳市龙华区观湖街道松轩社区虎地排126号锦绣二期4号楼B4层01-26号铺</t>
+          <t>深圳市龙岗区坂田街道环城南路9号高力特智慧能源产业园</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -11337,7 +11337,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>福州建发众驰4S中心</t>
+          <t>福州建发捷路4S中心</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -11352,7 +11352,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县上街镇源通东路63号</t>
+          <t>福建省福州市马尾区马尾镇马江路28号</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -11369,7 +11369,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>福州建发捷路4S中心</t>
+          <t>福州建发众驰4S中心</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -11384,7 +11384,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市马尾区马尾镇马江路28号</t>
+          <t>福建省福州市闽侯县上街镇源通东路63号</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -11802,22 +11802,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11827,29 +11827,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
+          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11859,29 +11859,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
+          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11891,29 +11891,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
+          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11923,29 +11923,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
+          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11955,29 +11955,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
+          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11987,29 +11987,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
+          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12019,7 +12019,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
+          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
         </is>
       </c>
     </row>
@@ -12031,17 +12031,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
+          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
@@ -12063,17 +12063,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12083,29 +12083,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
+          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12115,14 +12115,14 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
+          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
+          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
         </is>
       </c>
     </row>
@@ -12186,22 +12186,22 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12211,7 +12211,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
+          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
         </is>
       </c>
     </row>
@@ -12223,17 +12223,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12243,29 +12243,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
@@ -12314,22 +12314,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>奔驰</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>宜春华宏臻汽车有限公司</t>
+          <t>理想汽车鹿城零售中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>宜春华宏星汽车有限公司</t>
+          <t>理想汽车温州鹿城零售中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12346,22 +12346,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>奔驰</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车铜仁万山授权钣喷中心（俊汇店）</t>
+          <t>宜春华宏臻汽车有限公司</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车铜仁万山授权服务中心（俊汇店）</t>
+          <t>宜春华宏星汽车有限公司</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12378,22 +12378,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鹿城零售中心</t>
+          <t>天津鲁能城城市中心店</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州鹿城零售中心</t>
+          <t>天津贵和城市中心店</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12410,22 +12410,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>天津鲁能城城市中心店</t>
+          <t>理想汽车铜仁万山授权钣喷中心（俊汇店）</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>天津贵和城市中心店</t>
+          <t>理想汽车铜仁万山授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（24家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（25家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（23条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="新增网点（24家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="减少网点（25家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="变更明细（23条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -11177,7 +11177,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙华锦绣科学园服务中心</t>
+          <t>小鹏汽车深圳坂田环城南路服务中心</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -11192,7 +11192,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>广东省深圳市龙华区观湖街道松轩社区虎地排126号锦绣二期4号楼B4层01-26号铺</t>
+          <t>深圳市龙岗区坂田街道环城南路9号高力特智慧能源产业园</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -11209,7 +11209,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田环城南路服务中心</t>
+          <t>小鹏汽车深圳龙华锦绣科学园服务中心</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -11224,7 +11224,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>深圳市龙岗区坂田街道环城南路9号高力特智慧能源产业园</t>
+          <t>广东省深圳市龙华区观湖街道松轩社区虎地排126号锦绣二期4号楼B4层01-26号铺</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -11657,7 +11657,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁北京</t>
+          <t>阿斯顿·马丁北京售后服务中心</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11672,7 +11672,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>东城区金宝街99号 , 北京, 100005</t>
+          <t>大兴区金时大街7号院5号楼, 北京, 100076</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁北京售后服务中心</t>
+          <t>阿斯顿·马丁北京</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>大兴区金时大街7号院5号楼, 北京, 100076</t>
+          <t>东城区金宝街99号 , 北京, 100005</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -11802,22 +11802,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11827,29 +11827,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11859,29 +11859,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
+          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11891,14 +11891,14 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
+          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -11908,12 +11908,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11923,7 +11923,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
+          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
         </is>
       </c>
     </row>
@@ -11935,17 +11935,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11955,29 +11955,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
+          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
+          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
         </is>
       </c>
     </row>
@@ -11999,17 +11999,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12019,29 +12019,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
+          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12051,29 +12051,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
+          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12083,14 +12083,14 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
+          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -12100,12 +12100,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12115,29 +12115,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
+          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12147,14 +12147,14 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
+          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12179,29 +12179,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
+          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12211,29 +12211,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
+          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
+          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
         </is>
       </c>
     </row>
@@ -12255,17 +12255,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
         </is>
       </c>
     </row>
@@ -12314,22 +12314,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>奔驰</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鹿城零售中心</t>
+          <t>宜春华宏臻汽车有限公司</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州鹿城零售中心</t>
+          <t>宜春华宏星汽车有限公司</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12346,22 +12346,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>奔驰</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>宜春华宏臻汽车有限公司</t>
+          <t>天津鲁能城城市中心店</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>宜春华宏星汽车有限公司</t>
+          <t>天津贵和城市中心店</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12378,22 +12378,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>天津鲁能城城市中心店</t>
+          <t>理想汽车铜仁万山授权钣喷中心（俊汇店）</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>天津贵和城市中心店</t>
+          <t>理想汽车铜仁万山授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12415,17 +12415,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车铜仁万山授权钣喷中心（俊汇店）</t>
+          <t>理想汽车鹿城零售中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车铜仁万山授权服务中心（俊汇店）</t>
+          <t>理想汽车温州鹿城零售中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
@@ -11337,7 +11337,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>福州建发捷路4S中心</t>
+          <t>福州建发众驰4S中心</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -11352,7 +11352,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市马尾区马尾镇马江路28号</t>
+          <t>福建省福州市闽侯县上街镇源通东路63号</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -11369,7 +11369,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>福州建发众驰4S中心</t>
+          <t>福州建发捷路4S中心</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -11384,7 +11384,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县上街镇源通东路63号</t>
+          <t>福建省福州市马尾区马尾镇马江路28号</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -11657,7 +11657,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁北京售后服务中心</t>
+          <t>阿斯顿·马丁北京</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11672,7 +11672,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>大兴区金时大街7号院5号楼, 北京, 100076</t>
+          <t>东城区金宝街99号 , 北京, 100005</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁北京</t>
+          <t>阿斯顿·马丁北京售后服务中心</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>东城区金宝街99号 , 北京, 100005</t>
+          <t>大兴区金时大街7号院5号楼, 北京, 100076</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -11807,17 +11807,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11827,29 +11827,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11859,29 +11859,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
+          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
+          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
         </is>
       </c>
     </row>
@@ -11903,17 +11903,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11923,29 +11923,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
+          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
+          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
         </is>
       </c>
     </row>
@@ -11994,22 +11994,22 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12019,29 +12019,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
+          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12051,29 +12051,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
+          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12083,29 +12083,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
+          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12115,29 +12115,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
+          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
@@ -12159,17 +12159,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
+          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
         </is>
       </c>
     </row>
@@ -12218,22 +12218,22 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12243,29 +12243,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
+          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
+          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
         </is>
       </c>
     </row>
@@ -12346,22 +12346,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>天津鲁能城城市中心店</t>
+          <t>理想汽车鹿城零售中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>天津贵和城市中心店</t>
+          <t>理想汽车温州鹿城零售中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12410,22 +12410,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鹿城零售中心</t>
+          <t>天津鲁能城城市中心店</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州鹿城零售中心</t>
+          <t>天津贵和城市中心店</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12474,22 +12474,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小米汽车上海松江区松江印象城</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环服务中心</t>
+          <t>小米之家上海市松江区松江印象城汽车体验店</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12499,29 +12499,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 88%</t>
+          <t>店名相似度 77%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海松江区松江印象城</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市松江区松江印象城汽车体验店</t>
+          <t>小鹏汽车周口南环服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -12531,7 +12531,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 77%</t>
+          <t>店名相似度 88%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="新增网点（24家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="减少网点（25家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="变更明细（23条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（24家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（25家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（23条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -11177,7 +11177,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田环城南路服务中心</t>
+          <t>小鹏汽车深圳龙华锦绣科学园服务中心</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -11192,7 +11192,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>深圳市龙岗区坂田街道环城南路9号高力特智慧能源产业园</t>
+          <t>广东省深圳市龙华区观湖街道松轩社区虎地排126号锦绣二期4号楼B4层01-26号铺</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -11209,7 +11209,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙华锦绣科学园服务中心</t>
+          <t>小鹏汽车深圳坂田环城南路服务中心</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -11224,7 +11224,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>广东省深圳市龙华区观湖街道松轩社区虎地排126号锦绣二期4号楼B4层01-26号铺</t>
+          <t>深圳市龙岗区坂田街道环城南路9号高力特智慧能源产业园</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -11802,22 +11802,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11827,29 +11827,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
+          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11859,29 +11859,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
+          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
+          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
         </is>
       </c>
     </row>
@@ -11903,17 +11903,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11923,29 +11923,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
+          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
+          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
         </is>
       </c>
     </row>
@@ -11967,17 +11967,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
@@ -11999,17 +11999,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12019,29 +12019,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
+          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12051,29 +12051,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
+          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12083,7 +12083,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
+          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
         </is>
       </c>
     </row>
@@ -12095,17 +12095,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12115,7 +12115,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
+          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
         </is>
       </c>
     </row>
@@ -12127,17 +12127,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
@@ -12186,22 +12186,22 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12211,29 +12211,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
+          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12243,29 +12243,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
+          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
+          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
         </is>
       </c>
     </row>
@@ -12314,22 +12314,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>奔驰</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>宜春华宏臻汽车有限公司</t>
+          <t>理想汽车铜仁万山授权钣喷中心（俊汇店）</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>宜春华宏星汽车有限公司</t>
+          <t>理想汽车铜仁万山授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12346,22 +12346,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>奔驰</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鹿城零售中心</t>
+          <t>宜春华宏臻汽车有限公司</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州鹿城零售中心</t>
+          <t>宜春华宏星汽车有限公司</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12378,22 +12378,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车铜仁万山授权钣喷中心（俊汇店）</t>
+          <t>天津鲁能城城市中心店</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车铜仁万山授权服务中心（俊汇店）</t>
+          <t>天津贵和城市中心店</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12410,22 +12410,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>天津鲁能城城市中心店</t>
+          <t>理想汽车鹿城零售中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>天津贵和城市中心店</t>
+          <t>理想汽车温州鹿城零售中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12474,22 +12474,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海松江区松江印象城</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市松江区松江印象城汽车体验店</t>
+          <t>小鹏汽车周口南环服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12499,29 +12499,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 77%</t>
+          <t>店名相似度 88%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小米汽车上海松江区松江印象城</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环服务中心</t>
+          <t>小米之家上海市松江区松江印象城汽车体验店</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -12531,7 +12531,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 88%</t>
+          <t>店名相似度 77%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（24家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（25家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（23条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="新增网点（24家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="减少网点（25家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="变更明细（23条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -11337,7 +11337,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>福州建发众驰4S中心</t>
+          <t>福州建发捷路4S中心</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -11352,7 +11352,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县上街镇源通东路63号</t>
+          <t>福建省福州市马尾区马尾镇马江路28号</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -11369,7 +11369,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>福州建发捷路4S中心</t>
+          <t>福州建发众驰4S中心</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -11384,7 +11384,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市马尾区马尾镇马江路28号</t>
+          <t>福建省福州市闽侯县上街镇源通东路63号</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -11657,7 +11657,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁北京</t>
+          <t>阿斯顿·马丁北京售后服务中心</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11672,7 +11672,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>东城区金宝街99号 , 北京, 100005</t>
+          <t>大兴区金时大街7号院5号楼, 北京, 100076</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁北京售后服务中心</t>
+          <t>阿斯顿·马丁北京</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>大兴区金时大街7号院5号楼, 北京, 100076</t>
+          <t>东城区金宝街99号 , 北京, 100005</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -11802,22 +11802,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11827,29 +11827,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
+          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
+          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
         </is>
       </c>
     </row>
@@ -11871,17 +11871,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11891,29 +11891,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
+          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11923,7 +11923,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
+          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
         </is>
       </c>
     </row>
@@ -11935,17 +11935,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
+          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
         </is>
       </c>
     </row>
@@ -11967,17 +11967,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
         </is>
       </c>
     </row>
@@ -12004,12 +12004,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12019,29 +12019,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
+          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12051,29 +12051,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
+          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12083,14 +12083,14 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
+          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -12100,12 +12100,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12115,29 +12115,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
+          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12147,29 +12147,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
+          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12179,29 +12179,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
+          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12211,29 +12211,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
+          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
+          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
@@ -12255,17 +12255,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
@@ -12314,22 +12314,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>理想汽车铜仁万山授权钣喷中心（俊汇店）</t>
+          <t>天津鲁能城城市中心店</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>理想汽车铜仁万山授权服务中心（俊汇店）</t>
+          <t>天津贵和城市中心店</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12346,22 +12346,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>奔驰</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>宜春华宏臻汽车有限公司</t>
+          <t>理想汽车鹿城零售中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>宜春华宏星汽车有限公司</t>
+          <t>理想汽车温州鹿城零售中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12378,22 +12378,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>天津鲁能城城市中心店</t>
+          <t>理想汽车铜仁万山授权钣喷中心（俊汇店）</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>天津贵和城市中心店</t>
+          <t>理想汽车铜仁万山授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12410,22 +12410,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>奔驰</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鹿城零售中心</t>
+          <t>宜春华宏臻汽车有限公司</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州鹿城零售中心</t>
+          <t>宜春华宏星汽车有限公司</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
@@ -11177,7 +11177,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙华锦绣科学园服务中心</t>
+          <t>小鹏汽车深圳坂田环城南路服务中心</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -11192,7 +11192,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>广东省深圳市龙华区观湖街道松轩社区虎地排126号锦绣二期4号楼B4层01-26号铺</t>
+          <t>深圳市龙岗区坂田街道环城南路9号高力特智慧能源产业园</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -11209,7 +11209,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田环城南路服务中心</t>
+          <t>小鹏汽车深圳龙华锦绣科学园服务中心</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -11224,7 +11224,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>深圳市龙岗区坂田街道环城南路9号高力特智慧能源产业园</t>
+          <t>广东省深圳市龙华区观湖街道松轩社区虎地排126号锦绣二期4号楼B4层01-26号铺</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -11657,7 +11657,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁北京售后服务中心</t>
+          <t>阿斯顿·马丁北京</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11672,7 +11672,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>大兴区金时大街7号院5号楼, 北京, 100076</t>
+          <t>东城区金宝街99号 , 北京, 100005</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁北京</t>
+          <t>阿斯顿·马丁北京售后服务中心</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>东城区金宝街99号 , 北京, 100005</t>
+          <t>大兴区金时大街7号院5号楼, 北京, 100076</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -11807,17 +11807,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11827,29 +11827,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
+          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
+          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
         </is>
       </c>
     </row>
@@ -11871,17 +11871,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11891,29 +11891,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
+          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11923,29 +11923,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
+          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
+          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
         </is>
       </c>
     </row>
@@ -11967,17 +11967,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
+          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
         </is>
       </c>
     </row>
@@ -11999,17 +11999,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12019,29 +12019,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
+          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12051,29 +12051,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
+          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12083,29 +12083,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
+          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12115,29 +12115,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
+          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
+          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
@@ -12159,17 +12159,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
@@ -12191,17 +12191,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12211,29 +12211,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
+          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12243,29 +12243,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
+          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
         </is>
       </c>
     </row>
@@ -12314,22 +12314,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>天津鲁能城城市中心店</t>
+          <t>理想汽车铜仁万山授权钣喷中心（俊汇店）</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>天津贵和城市中心店</t>
+          <t>理想汽车铜仁万山授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12346,22 +12346,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鹿城零售中心</t>
+          <t>天津鲁能城城市中心店</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州鹿城零售中心</t>
+          <t>天津贵和城市中心店</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12378,22 +12378,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>奔驰</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车铜仁万山授权钣喷中心（俊汇店）</t>
+          <t>宜春华宏臻汽车有限公司</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车铜仁万山授权服务中心（俊汇店）</t>
+          <t>宜春华宏星汽车有限公司</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12410,22 +12410,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>奔驰</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>宜春华宏臻汽车有限公司</t>
+          <t>理想汽车鹿城零售中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>宜春华宏星汽车有限公司</t>
+          <t>理想汽车温州鹿城零售中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12474,22 +12474,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小米汽车上海松江区松江印象城</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环服务中心</t>
+          <t>小米之家上海市松江区松江印象城汽车体验店</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12499,29 +12499,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 88%</t>
+          <t>店名相似度 77%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海松江区松江印象城</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市松江区松江印象城汽车体验店</t>
+          <t>小鹏汽车周口南环服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -12531,7 +12531,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 77%</t>
+          <t>店名相似度 88%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
@@ -11657,7 +11657,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁北京</t>
+          <t>阿斯顿·马丁北京售后服务中心</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11672,7 +11672,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>东城区金宝街99号 , 北京, 100005</t>
+          <t>大兴区金时大街7号院5号楼, 北京, 100076</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁北京售后服务中心</t>
+          <t>阿斯顿·马丁北京</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>大兴区金时大街7号院5号楼, 北京, 100076</t>
+          <t>东城区金宝街99号 , 北京, 100005</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -11802,22 +11802,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11827,29 +11827,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
+          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
+          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
         </is>
       </c>
     </row>
@@ -11871,17 +11871,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11891,14 +11891,14 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
+          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -11908,12 +11908,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11923,29 +11923,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
+          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
+          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
         </is>
       </c>
     </row>
@@ -11967,17 +11967,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11987,29 +11987,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
+          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12019,7 +12019,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
+          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
         </is>
       </c>
     </row>
@@ -12068,12 +12068,12 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12083,7 +12083,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
+          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
         </is>
       </c>
     </row>
@@ -12095,17 +12095,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12115,7 +12115,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
+          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
         </is>
       </c>
     </row>
@@ -12127,17 +12127,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12147,29 +12147,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12179,29 +12179,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12211,29 +12211,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
+          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12243,14 +12243,14 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
+          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
+          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
         </is>
       </c>
     </row>
@@ -12319,17 +12319,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>理想汽车铜仁万山授权钣喷中心（俊汇店）</t>
+          <t>理想汽车鹿城零售中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>理想汽车铜仁万山授权服务中心（俊汇店）</t>
+          <t>理想汽车温州鹿城零售中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12415,17 +12415,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鹿城零售中心</t>
+          <t>理想汽车铜仁万山授权钣喷中心（俊汇店）</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州鹿城零售中心</t>
+          <t>理想汽车铜仁万山授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12474,22 +12474,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海松江区松江印象城</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市松江区松江印象城汽车体验店</t>
+          <t>小鹏汽车周口南环服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12499,29 +12499,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 77%</t>
+          <t>店名相似度 88%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小米汽车上海松江区松江印象城</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环服务中心</t>
+          <t>小米之家上海市松江区松江印象城汽车体验店</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -12531,7 +12531,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 88%</t>
+          <t>店名相似度 77%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
@@ -11802,22 +11802,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11827,29 +11827,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
+          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11859,29 +11859,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
+          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11891,29 +11891,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
+          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11923,29 +11923,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
+          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
+          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
         </is>
       </c>
     </row>
@@ -11967,17 +11967,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11987,29 +11987,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
+          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12019,7 +12019,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
+          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
         </is>
       </c>
     </row>
@@ -12031,17 +12031,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
@@ -12063,17 +12063,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12083,7 +12083,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
+          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
         </is>
       </c>
     </row>
@@ -12095,17 +12095,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12115,7 +12115,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
+          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
         </is>
       </c>
     </row>
@@ -12127,17 +12127,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12147,29 +12147,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12179,29 +12179,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
+          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12211,29 +12211,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
+          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12243,29 +12243,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
+          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
+          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
         </is>
       </c>
     </row>
@@ -12319,17 +12319,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鹿城零售中心</t>
+          <t>理想汽车铜仁万山授权钣喷中心（俊汇店）</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州鹿城零售中心</t>
+          <t>理想汽车铜仁万山授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12346,22 +12346,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>天津鲁能城城市中心店</t>
+          <t>理想汽车鹿城零售中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>天津贵和城市中心店</t>
+          <t>理想汽车温州鹿城零售中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12410,22 +12410,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车铜仁万山授权钣喷中心（俊汇店）</t>
+          <t>天津鲁能城城市中心店</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车铜仁万山授权服务中心（俊汇店）</t>
+          <t>天津贵和城市中心店</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
@@ -11177,7 +11177,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田环城南路服务中心</t>
+          <t>小鹏汽车深圳龙华锦绣科学园服务中心</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -11192,7 +11192,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>深圳市龙岗区坂田街道环城南路9号高力特智慧能源产业园</t>
+          <t>广东省深圳市龙华区观湖街道松轩社区虎地排126号锦绣二期4号楼B4层01-26号铺</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -11209,7 +11209,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙华锦绣科学园服务中心</t>
+          <t>小鹏汽车深圳坂田环城南路服务中心</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -11224,7 +11224,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>广东省深圳市龙华区观湖街道松轩社区虎地排126号锦绣二期4号楼B4层01-26号铺</t>
+          <t>深圳市龙岗区坂田街道环城南路9号高力特智慧能源产业园</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -11337,7 +11337,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>福州建发捷路4S中心</t>
+          <t>福州建发众驰4S中心</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -11352,7 +11352,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市马尾区马尾镇马江路28号</t>
+          <t>福建省福州市闽侯县上街镇源通东路63号</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -11369,7 +11369,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>福州建发众驰4S中心</t>
+          <t>福州建发捷路4S中心</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -11384,7 +11384,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县上街镇源通东路63号</t>
+          <t>福建省福州市马尾区马尾镇马江路28号</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -11657,7 +11657,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁北京售后服务中心</t>
+          <t>阿斯顿·马丁北京</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11672,7 +11672,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>大兴区金时大街7号院5号楼, 北京, 100076</t>
+          <t>东城区金宝街99号 , 北京, 100005</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁北京</t>
+          <t>阿斯顿·马丁北京售后服务中心</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>东城区金宝街99号 , 北京, 100005</t>
+          <t>大兴区金时大街7号院5号楼, 北京, 100076</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -11802,22 +11802,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11827,29 +11827,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
+          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11859,29 +11859,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
+          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
+          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
         </is>
       </c>
     </row>
@@ -11903,17 +11903,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11923,29 +11923,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
+          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
+          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
         </is>
       </c>
     </row>
@@ -11994,22 +11994,22 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12019,29 +12019,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
+          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
         </is>
       </c>
     </row>
@@ -12063,17 +12063,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12083,29 +12083,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
+          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12115,7 +12115,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
+          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
         </is>
       </c>
     </row>
@@ -12127,17 +12127,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
+          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
         </is>
       </c>
     </row>
@@ -12191,17 +12191,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12211,14 +12211,14 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -12228,12 +12228,12 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
+          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
         </is>
       </c>
     </row>
@@ -12255,17 +12255,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
+          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
         </is>
       </c>
     </row>
@@ -12319,17 +12319,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>理想汽车铜仁万山授权钣喷中心（俊汇店）</t>
+          <t>理想汽车鹿城零售中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>理想汽车铜仁万山授权服务中心（俊汇店）</t>
+          <t>理想汽车温州鹿城零售中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12346,22 +12346,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>奔驰</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鹿城零售中心</t>
+          <t>宜春华宏臻汽车有限公司</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州鹿城零售中心</t>
+          <t>宜春华宏星汽车有限公司</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12378,22 +12378,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>奔驰</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>宜春华宏臻汽车有限公司</t>
+          <t>天津鲁能城城市中心店</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>宜春华宏星汽车有限公司</t>
+          <t>天津贵和城市中心店</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12410,22 +12410,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>天津鲁能城城市中心店</t>
+          <t>理想汽车铜仁万山授权钣喷中心（俊汇店）</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>天津贵和城市中心店</t>
+          <t>理想汽车铜仁万山授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
